--- a/Aero stuff/naca4415_xyzcords.xlsx
+++ b/Aero stuff/naca4415_xyzcords.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henjo\Documents\GitHub\Fixed_Wing_Capstone\Aero stuff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4BDA02-FD0D-4198-AA85-EB23D1967EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F17A0D-A56C-4469-8274-123EFC935A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="3936" windowWidth="23256" windowHeight="12456" xr2:uid="{5F1A58D8-B9B4-4B7E-90E1-6F007361965E}"/>
   </bookViews>
@@ -33,6 +33,17 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>ct:</t>
+  </si>
+  <si>
+    <t>cr:</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -411,10 +422,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4050CC7B-F371-48F1-B713-360137551242}">
-  <dimension ref="A1:C201"/>
+  <dimension ref="A1:O201"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="1">
         <v>1</v>
       </c>
@@ -424,8 +435,42 @@
       <c r="C1">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1">
+        <v>204.9</v>
+      </c>
+      <c r="G1">
+        <f>$F$1*$A1</f>
+        <v>204.9</v>
+      </c>
+      <c r="H1">
+        <f>$F$1*$B1</f>
+        <v>0</v>
+      </c>
+      <c r="I1">
+        <v>0</v>
+      </c>
+      <c r="K1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L1">
+        <v>143.4</v>
+      </c>
+      <c r="M1">
+        <f>$L$1*$A1</f>
+        <v>143.4</v>
+      </c>
+      <c r="N1">
+        <f>$L$1*$B1</f>
+        <v>0</v>
+      </c>
+      <c r="O1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>0.99975999999999998</v>
       </c>
@@ -435,8 +480,30 @@
       <c r="C2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G2">
+        <f t="shared" ref="G2:G65" si="0">$F$1*$A2</f>
+        <v>204.85082399999999</v>
+      </c>
+      <c r="H2">
+        <f t="shared" ref="H2:H65" si="1">$F$1*$B2</f>
+        <v>1.6392E-2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <f t="shared" ref="M2:M65" si="2">$L$1*$A2</f>
+        <v>143.36558400000001</v>
+      </c>
+      <c r="N2">
+        <f t="shared" ref="N2:N65" si="3">$L$1*$B2</f>
+        <v>1.1472000000000001E-2</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>0.99903900000000001</v>
       </c>
@@ -446,8 +513,30 @@
       <c r="C3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G3">
+        <f t="shared" si="0"/>
+        <v>204.70309109999999</v>
+      </c>
+      <c r="H3">
+        <f t="shared" si="1"/>
+        <v>6.5158199999999999E-2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <f t="shared" si="2"/>
+        <v>143.26219260000002</v>
+      </c>
+      <c r="N3">
+        <f t="shared" si="3"/>
+        <v>4.5601200000000001E-2</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>0.997838</v>
       </c>
@@ -457,8 +546,30 @@
       <c r="C4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>204.4570062</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="1"/>
+        <v>0.14650350000000001</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="2"/>
+        <v>143.08996920000001</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="3"/>
+        <v>0.10253100000000001</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>0.99615799999999999</v>
       </c>
@@ -468,8 +579,30 @@
       <c r="C5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>204.11277419999999</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>0.26001809999999997</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="2"/>
+        <v>142.8490572</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="3"/>
+        <v>0.18197459999999999</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>0.99399999999999999</v>
       </c>
@@ -479,8 +612,30 @@
       <c r="C6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>203.67060000000001</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>0.40529220000000005</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="2"/>
+        <v>142.53960000000001</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="3"/>
+        <v>0.28364520000000004</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>0.99136599999999997</v>
       </c>
@@ -490,8 +645,30 @@
       <c r="C7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>203.13089339999999</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>0.58171110000000004</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="2"/>
+        <v>142.16188439999999</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="3"/>
+        <v>0.40711259999999999</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>0.988259</v>
       </c>
@@ -501,8 +678,30 @@
       <c r="C8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>202.4942691</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>0.78927480000000005</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="2"/>
+        <v>141.7163406</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="3"/>
+        <v>0.5523768</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>0.98468</v>
       </c>
@@ -512,8 +711,30 @@
       <c r="C9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>201.760932</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>1.0267538999999999</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="2"/>
+        <v>141.203112</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="3"/>
+        <v>0.71857740000000003</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>0.98063299999999998</v>
       </c>
@@ -523,8 +744,30 @@
       <c r="C10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>200.93170169999999</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>1.2937386</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="2"/>
+        <v>140.62277220000001</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="3"/>
+        <v>0.90542760000000011</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>0.97612100000000002</v>
       </c>
@@ -534,8 +777,30 @@
       <c r="C11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>200.00719290000001</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>1.5892044000000001</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="2"/>
+        <v>139.97575140000001</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="3"/>
+        <v>1.1122103999999999</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>0.97114699999999998</v>
       </c>
@@ -545,8 +810,30 @@
       <c r="C12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>198.98802029999999</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="1"/>
+        <v>1.9123317</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="2"/>
+        <v>139.26247979999999</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="3"/>
+        <v>1.3383521999999999</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>0.96571600000000002</v>
       </c>
@@ -556,8 +843,30 @@
       <c r="C13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>197.87520840000002</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>2.2623009000000001</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="2"/>
+        <v>138.48367440000001</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="3"/>
+        <v>1.5832794000000001</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>0.95983200000000002</v>
       </c>
@@ -567,8 +876,30 @@
       <c r="C14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>196.66957680000002</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="1"/>
+        <v>2.6376777000000002</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="2"/>
+        <v>137.6399088</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="3"/>
+        <v>1.8459882000000001</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>0.95350100000000004</v>
       </c>
@@ -578,8 +909,30 @@
       <c r="C15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>195.3723549</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>3.0378474000000004</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="2"/>
+        <v>136.73204340000001</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="3"/>
+        <v>2.1260484000000002</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>0.94672599999999996</v>
       </c>
@@ -589,8 +942,30 @@
       <c r="C16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>193.98415739999999</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>3.4609659000000002</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <f>$L$1*$A16</f>
+        <v>135.76050839999999</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="3"/>
+        <v>2.4221694</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>0.93951499999999999</v>
       </c>
@@ -600,8 +975,30 @@
       <c r="C17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>192.50662349999999</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="1"/>
+        <v>3.9064185</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="2"/>
+        <v>134.726451</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="3"/>
+        <v>2.733921</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>0.93187399999999998</v>
       </c>
@@ -611,8 +1008,30 @@
       <c r="C18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>190.94098260000001</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="1"/>
+        <v>4.372566</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="2"/>
+        <v>133.63073159999999</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="3"/>
+        <v>3.0601560000000001</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>0.92380799999999996</v>
       </c>
@@ -622,8 +1041,30 @@
       <c r="C19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>189.2882592</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="1"/>
+        <v>4.8579741000000007</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="2"/>
+        <v>132.47406720000001</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="3"/>
+        <v>3.3998706000000003</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>0.91532400000000003</v>
       </c>
@@ -633,8 +1074,30 @@
       <c r="C20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>187.54988760000001</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="1"/>
+        <v>5.3614134</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="2"/>
+        <v>131.2574616</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="3"/>
+        <v>3.7522044000000001</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>0.90643099999999999</v>
       </c>
@@ -644,8 +1107,30 @@
       <c r="C21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>185.7277119</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="1"/>
+        <v>5.8814495999999998</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="2"/>
+        <v>129.9822054</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="3"/>
+        <v>4.1161536000000005</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>0.89713600000000004</v>
       </c>
@@ -655,8 +1140,30 @@
       <c r="C22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>183.82316640000002</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="1"/>
+        <v>6.4164435000000006</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="2"/>
+        <v>128.64930240000001</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="3"/>
+        <v>4.490571000000001</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>0.88744699999999999</v>
       </c>
@@ -666,8 +1173,30 @@
       <c r="C23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G23">
+        <f t="shared" si="0"/>
+        <v>181.8378903</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="1"/>
+        <v>6.9651657000000009</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="2"/>
+        <v>127.2598998</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="3"/>
+        <v>4.8745962000000009</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>0.87737200000000004</v>
       </c>
@@ -677,8 +1206,30 @@
       <c r="C24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G24">
+        <f t="shared" si="0"/>
+        <v>179.77352280000002</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="1"/>
+        <v>7.5259770000000001</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="2"/>
+        <v>125.81514480000001</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="3"/>
+        <v>5.2670820000000003</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>0.86692100000000005</v>
       </c>
@@ -688,8 +1239,30 @@
       <c r="C25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G25">
+        <f t="shared" si="0"/>
+        <v>177.63211290000001</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="1"/>
+        <v>8.0972381999999996</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="2"/>
+        <v>124.31647140000001</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="3"/>
+        <v>5.6668811999999997</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>0.85610299999999995</v>
       </c>
@@ -699,8 +1272,30 @@
       <c r="C26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G26">
+        <f t="shared" si="0"/>
+        <v>175.41550469999999</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="1"/>
+        <v>8.6773100999999997</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="2"/>
+        <v>122.7651702</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="3"/>
+        <v>6.0728466000000001</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>0.84492699999999998</v>
       </c>
@@ -710,8 +1305,30 @@
       <c r="C27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G27">
+        <f t="shared" si="0"/>
+        <v>173.12554230000001</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="1"/>
+        <v>9.2649632999999998</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="2"/>
+        <v>121.1625318</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="3"/>
+        <v>6.4841177999999999</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>0.83340400000000003</v>
       </c>
@@ -721,8 +1338,30 @@
       <c r="C28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G28">
+        <f t="shared" si="0"/>
+        <v>170.76447960000002</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="1"/>
+        <v>9.8585586000000003</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="2"/>
+        <v>119.5101336</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="3"/>
+        <v>6.8995476</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>0.82154499999999997</v>
       </c>
@@ -732,8 +1371,30 @@
       <c r="C29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G29">
+        <f t="shared" si="0"/>
+        <v>168.33457050000001</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="1"/>
+        <v>10.4562519</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="2"/>
+        <v>117.80955299999999</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="3"/>
+        <v>7.3178454000000004</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>0.80935999999999997</v>
       </c>
@@ -743,8 +1404,30 @@
       <c r="C30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G30">
+        <f t="shared" si="0"/>
+        <v>165.837864</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="1"/>
+        <v>11.0568138</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="2"/>
+        <v>116.062224</v>
+      </c>
+      <c r="N30">
+        <f t="shared" si="3"/>
+        <v>7.7381508000000006</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>0.79686000000000001</v>
       </c>
@@ -754,8 +1437,30 @@
       <c r="C31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G31">
+        <f t="shared" si="0"/>
+        <v>163.276614</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="1"/>
+        <v>11.658400199999999</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="2"/>
+        <v>114.26972400000001</v>
+      </c>
+      <c r="N31">
+        <f t="shared" si="3"/>
+        <v>8.1591731999999997</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>0.78405800000000003</v>
       </c>
@@ -765,8 +1470,30 @@
       <c r="C32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G32">
+        <f t="shared" si="0"/>
+        <v>160.65348420000001</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="1"/>
+        <v>12.259371900000001</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="2"/>
+        <v>112.43391720000001</v>
+      </c>
+      <c r="N32">
+        <f t="shared" si="3"/>
+        <v>8.5797654000000012</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>0.77096399999999998</v>
       </c>
@@ -776,8 +1503,30 @@
       <c r="C33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G33">
+        <f t="shared" si="0"/>
+        <v>157.97052360000001</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="1"/>
+        <v>12.858704400000002</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="2"/>
+        <v>110.5562376</v>
+      </c>
+      <c r="N33">
+        <f t="shared" si="3"/>
+        <v>8.9992104000000008</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>0.75759200000000004</v>
       </c>
@@ -787,8 +1536,30 @@
       <c r="C34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G34">
+        <f t="shared" si="0"/>
+        <v>155.23060080000002</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="1"/>
+        <v>13.454348700000001</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="2"/>
+        <v>108.63869280000002</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="3"/>
+        <v>9.4160742000000006</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>0.743954</v>
       </c>
@@ -798,8 +1569,30 @@
       <c r="C35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G35">
+        <f t="shared" si="0"/>
+        <v>152.43617460000002</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="1"/>
+        <v>14.0448705</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <f t="shared" si="2"/>
+        <v>106.68300360000001</v>
+      </c>
+      <c r="N35">
+        <f t="shared" si="3"/>
+        <v>9.8293529999999993</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>0.73006300000000002</v>
       </c>
@@ -809,8 +1602,30 @@
       <c r="C36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G36">
+        <f t="shared" si="0"/>
+        <v>149.5899087</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="1"/>
+        <v>14.628835500000001</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <f t="shared" si="2"/>
+        <v>104.6910342</v>
+      </c>
+      <c r="N36">
+        <f t="shared" si="3"/>
+        <v>10.238043000000001</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>0.71593200000000001</v>
       </c>
@@ -820,8 +1635,30 @@
       <c r="C37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G37">
+        <f t="shared" si="0"/>
+        <v>146.69446680000001</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="1"/>
+        <v>15.204809399999998</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <f t="shared" si="2"/>
+        <v>102.66464880000001</v>
+      </c>
+      <c r="N37">
+        <f t="shared" si="3"/>
+        <v>10.641140399999999</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>0.70157499999999995</v>
       </c>
@@ -831,8 +1668,30 @@
       <c r="C38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G38">
+        <f t="shared" si="0"/>
+        <v>143.75271749999999</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="1"/>
+        <v>15.771153</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="2"/>
+        <v>100.60585499999999</v>
+      </c>
+      <c r="N38">
+        <f t="shared" si="3"/>
+        <v>11.037497999999999</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>0.68700600000000001</v>
       </c>
@@ -842,8 +1701,30 @@
       <c r="C39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G39">
+        <f t="shared" si="0"/>
+        <v>140.7675294</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="1"/>
+        <v>16.3266369</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="2"/>
+        <v>98.516660400000006</v>
+      </c>
+      <c r="N39">
+        <f t="shared" si="3"/>
+        <v>11.426255400000001</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>0.672238</v>
       </c>
@@ -853,8 +1734,30 @@
       <c r="C40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G40">
+        <f t="shared" si="0"/>
+        <v>137.74156619999999</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="1"/>
+        <v>16.869417000000002</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <f t="shared" si="2"/>
+        <v>96.398929199999998</v>
+      </c>
+      <c r="N40">
+        <f t="shared" si="3"/>
+        <v>11.806122</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>0.65728699999999995</v>
       </c>
@@ -864,8 +1767,30 @@
       <c r="C41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G41">
+        <f t="shared" si="0"/>
+        <v>134.6781063</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="1"/>
+        <v>17.3986737</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <f t="shared" si="2"/>
+        <v>94.254955799999991</v>
+      </c>
+      <c r="N41">
+        <f t="shared" si="3"/>
+        <v>12.176524200000001</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>0.64216700000000004</v>
       </c>
@@ -875,8 +1800,30 @@
       <c r="C42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G42">
+        <f t="shared" si="0"/>
+        <v>131.58001830000001</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="1"/>
+        <v>17.912562900000001</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="2"/>
+        <v>92.086747800000012</v>
+      </c>
+      <c r="N42">
+        <f t="shared" si="3"/>
+        <v>12.536171400000001</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>0.62689300000000003</v>
       </c>
@@ -886,8 +1833,30 @@
       <c r="C43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G43">
+        <f t="shared" si="0"/>
+        <v>128.45037570000002</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="1"/>
+        <v>18.409855199999999</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <f t="shared" si="2"/>
+        <v>89.896456200000003</v>
+      </c>
+      <c r="N43">
+        <f t="shared" si="3"/>
+        <v>12.8842032</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>0.61148000000000002</v>
       </c>
@@ -897,8 +1866,30 @@
       <c r="C44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G44">
+        <f t="shared" si="0"/>
+        <v>125.292252</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="1"/>
+        <v>18.889116300000001</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <f t="shared" si="2"/>
+        <v>87.686232000000004</v>
+      </c>
+      <c r="N44">
+        <f t="shared" si="3"/>
+        <v>13.219615800000001</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>0.595943</v>
       </c>
@@ -908,8 +1899,30 @@
       <c r="C45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G45">
+        <f t="shared" si="0"/>
+        <v>122.10872070000001</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="1"/>
+        <v>19.349321700000001</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <f t="shared" si="2"/>
+        <v>85.458226199999999</v>
+      </c>
+      <c r="N45">
+        <f t="shared" si="3"/>
+        <v>13.541692200000002</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A46">
         <v>0.58029799999999998</v>
       </c>
@@ -919,8 +1932,30 @@
       <c r="C46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G46">
+        <f t="shared" si="0"/>
+        <v>118.9030602</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="1"/>
+        <v>19.789037100000002</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <f t="shared" si="2"/>
+        <v>83.214733199999998</v>
+      </c>
+      <c r="N46">
+        <f t="shared" si="3"/>
+        <v>13.8494286</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A47">
         <v>0.56456099999999998</v>
       </c>
@@ -930,8 +1965,30 @@
       <c r="C47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G47">
+        <f t="shared" si="0"/>
+        <v>115.6785489</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="1"/>
+        <v>20.207238</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <f t="shared" si="2"/>
+        <v>80.958047399999998</v>
+      </c>
+      <c r="N47">
+        <f t="shared" si="3"/>
+        <v>14.142108</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A48">
         <v>0.54874800000000001</v>
       </c>
@@ -941,8 +1998,30 @@
       <c r="C48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G48">
+        <f t="shared" si="0"/>
+        <v>112.43846520000001</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="1"/>
+        <v>20.602285200000001</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <f t="shared" si="2"/>
+        <v>78.690463200000011</v>
+      </c>
+      <c r="N48">
+        <f t="shared" si="3"/>
+        <v>14.4185832</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A49">
         <v>0.53287399999999996</v>
       </c>
@@ -952,8 +2031,30 @@
       <c r="C49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G49">
+        <f t="shared" si="0"/>
+        <v>109.1858826</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="1"/>
+        <v>20.973564000000003</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <f t="shared" si="2"/>
+        <v>76.41413159999999</v>
+      </c>
+      <c r="N49">
+        <f t="shared" si="3"/>
+        <v>14.678424000000001</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A50">
         <v>0.51695599999999997</v>
       </c>
@@ -963,8 +2064,30 @@
       <c r="C50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G50">
+        <f t="shared" si="0"/>
+        <v>105.92428439999999</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="1"/>
+        <v>21.319640100000001</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <f t="shared" si="2"/>
+        <v>74.131490400000004</v>
+      </c>
+      <c r="N50">
+        <f t="shared" si="3"/>
+        <v>14.9206266</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A51">
         <v>0.50101099999999998</v>
       </c>
@@ -974,8 +2097,30 @@
       <c r="C51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G51">
+        <f t="shared" si="0"/>
+        <v>102.6571539</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="1"/>
+        <v>21.639489000000001</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <f t="shared" si="2"/>
+        <v>71.844977400000005</v>
+      </c>
+      <c r="N51">
+        <f t="shared" si="3"/>
+        <v>15.144474000000001</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A52">
         <v>0.48505500000000001</v>
       </c>
@@ -985,8 +2130,30 @@
       <c r="C52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G52">
+        <f t="shared" si="0"/>
+        <v>99.387769500000005</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="1"/>
+        <v>21.9322911</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <f t="shared" si="2"/>
+        <v>69.556887000000003</v>
+      </c>
+      <c r="N52">
+        <f t="shared" si="3"/>
+        <v>15.3493926</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A53">
         <v>0.46910400000000002</v>
       </c>
@@ -996,8 +2163,30 @@
       <c r="C53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G53">
+        <f t="shared" si="0"/>
+        <v>96.119409600000012</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="1"/>
+        <v>22.197021899999999</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <f t="shared" si="2"/>
+        <v>67.26951360000001</v>
+      </c>
+      <c r="N53">
+        <f t="shared" si="3"/>
+        <v>15.5346654</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A54">
         <v>0.45317499999999999</v>
       </c>
@@ -1007,8 +2196,30 @@
       <c r="C54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G54">
+        <f t="shared" si="0"/>
+        <v>92.855557500000003</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="1"/>
+        <v>22.432656900000001</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <f t="shared" si="2"/>
+        <v>64.985295000000008</v>
+      </c>
+      <c r="N54">
+        <f t="shared" si="3"/>
+        <v>15.699575400000001</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A55">
         <v>0.43725599999999998</v>
       </c>
@@ -1018,8 +2229,30 @@
       <c r="C55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G55">
+        <f t="shared" si="0"/>
+        <v>89.593754399999995</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="1"/>
+        <v>22.6385814</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <f t="shared" si="2"/>
+        <v>62.702510400000001</v>
+      </c>
+      <c r="N55">
+        <f t="shared" si="3"/>
+        <v>15.8436924</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A56">
         <v>0.42124499999999998</v>
       </c>
@@ -1029,8 +2262,30 @@
       <c r="C56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G56">
+        <f t="shared" si="0"/>
+        <v>86.313100500000004</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="1"/>
+        <v>22.808443499999999</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <f t="shared" si="2"/>
+        <v>60.406533000000003</v>
+      </c>
+      <c r="N56">
+        <f t="shared" si="3"/>
+        <v>15.962571000000001</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A57">
         <v>0.405304</v>
       </c>
@@ -1040,8 +2295,30 @@
       <c r="C57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G57">
+        <f t="shared" si="0"/>
+        <v>83.046789599999997</v>
+      </c>
+      <c r="H57">
+        <f t="shared" si="1"/>
+        <v>22.938964800000001</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <f t="shared" si="2"/>
+        <v>58.120593599999999</v>
+      </c>
+      <c r="N57">
+        <f t="shared" si="3"/>
+        <v>16.0539168</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A58">
         <v>0.38945000000000002</v>
       </c>
@@ -1051,8 +2328,30 @@
       <c r="C58">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G58">
+        <f t="shared" si="0"/>
+        <v>79.798304999999999</v>
+      </c>
+      <c r="H58">
+        <f t="shared" si="1"/>
+        <v>23.029735500000001</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <f t="shared" si="2"/>
+        <v>55.847130000000007</v>
+      </c>
+      <c r="N58">
+        <f t="shared" si="3"/>
+        <v>16.117443000000002</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A59">
         <v>0.37370100000000001</v>
       </c>
@@ -1062,8 +2361,30 @@
       <c r="C59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G59">
+        <f t="shared" si="0"/>
+        <v>76.571334899999997</v>
+      </c>
+      <c r="H59">
+        <f t="shared" si="1"/>
+        <v>23.080345800000003</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <f t="shared" si="2"/>
+        <v>53.588723400000006</v>
+      </c>
+      <c r="N59">
+        <f t="shared" si="3"/>
+        <v>16.152862800000001</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A60">
         <v>0.358074</v>
       </c>
@@ -1073,8 +2394,30 @@
       <c r="C60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G60">
+        <f t="shared" si="0"/>
+        <v>73.369362600000002</v>
+      </c>
+      <c r="H60">
+        <f t="shared" si="1"/>
+        <v>23.090590800000001</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <f t="shared" si="2"/>
+        <v>51.3478116</v>
+      </c>
+      <c r="N60">
+        <f t="shared" si="3"/>
+        <v>16.1600328</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A61">
         <v>0.342586</v>
       </c>
@@ -1084,8 +2427,30 @@
       <c r="C61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G61">
+        <f t="shared" si="0"/>
+        <v>70.195871400000001</v>
+      </c>
+      <c r="H61">
+        <f t="shared" si="1"/>
+        <v>23.060265600000001</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <f t="shared" si="2"/>
+        <v>49.126832400000005</v>
+      </c>
+      <c r="N61">
+        <f t="shared" si="3"/>
+        <v>16.138809600000002</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A62">
         <v>0.32725599999999999</v>
       </c>
@@ -1095,8 +2460,30 @@
       <c r="C62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G62">
+        <f t="shared" si="0"/>
+        <v>67.054754399999993</v>
+      </c>
+      <c r="H62">
+        <f t="shared" si="1"/>
+        <v>22.989370200000003</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <f t="shared" si="2"/>
+        <v>46.9285104</v>
+      </c>
+      <c r="N62">
+        <f t="shared" si="3"/>
+        <v>16.0891932</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A63">
         <v>0.31210100000000002</v>
       </c>
@@ -1106,8 +2493,30 @@
       <c r="C63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G63">
+        <f t="shared" si="0"/>
+        <v>63.949494900000005</v>
+      </c>
+      <c r="H63">
+        <f t="shared" si="1"/>
+        <v>22.878314400000001</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <f t="shared" si="2"/>
+        <v>44.755283400000003</v>
+      </c>
+      <c r="N63">
+        <f t="shared" si="3"/>
+        <v>16.0114704</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A64">
         <v>0.29713800000000001</v>
       </c>
@@ -1117,8 +2526,30 @@
       <c r="C64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G64">
+        <f t="shared" si="0"/>
+        <v>60.883576200000007</v>
+      </c>
+      <c r="H64">
+        <f t="shared" si="1"/>
+        <v>22.7270982</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <f t="shared" si="2"/>
+        <v>42.609589200000002</v>
+      </c>
+      <c r="N64">
+        <f t="shared" si="3"/>
+        <v>15.905641200000002</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A65">
         <v>0.28238400000000002</v>
       </c>
@@ -1128,8 +2559,30 @@
       <c r="C65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G65">
+        <f t="shared" si="0"/>
+        <v>57.860481600000007</v>
+      </c>
+      <c r="H65">
+        <f t="shared" si="1"/>
+        <v>22.536131400000002</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <f t="shared" si="2"/>
+        <v>40.493865600000007</v>
+      </c>
+      <c r="N65">
+        <f t="shared" si="3"/>
+        <v>15.7719924</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A66">
         <v>0.26785500000000001</v>
       </c>
@@ -1139,8 +2592,30 @@
       <c r="C66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G66">
+        <f t="shared" ref="G66:G129" si="4">$F$1*$A66</f>
+        <v>54.883489500000003</v>
+      </c>
+      <c r="H66">
+        <f t="shared" ref="H66:H129" si="5">$F$1*$B66</f>
+        <v>22.305823800000002</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <f t="shared" ref="M66:M129" si="6">$L$1*$A66</f>
+        <v>38.410407000000006</v>
+      </c>
+      <c r="N66">
+        <f t="shared" ref="N66:N129" si="7">$L$1*$B66</f>
+        <v>15.610810800000001</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A67">
         <v>0.25356899999999999</v>
       </c>
@@ -1150,8 +2625,30 @@
       <c r="C67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G67">
+        <f t="shared" si="4"/>
+        <v>51.956288100000002</v>
+      </c>
+      <c r="H67">
+        <f t="shared" si="5"/>
+        <v>22.036995000000001</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <f t="shared" si="6"/>
+        <v>36.361794600000003</v>
+      </c>
+      <c r="N67">
+        <f t="shared" si="7"/>
+        <v>15.422670000000002</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A68">
         <v>0.239541</v>
       </c>
@@ -1161,8 +2658,30 @@
       <c r="C68">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G68">
+        <f t="shared" si="4"/>
+        <v>49.081950900000002</v>
+      </c>
+      <c r="H68">
+        <f t="shared" si="5"/>
+        <v>21.730464600000001</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <f t="shared" si="6"/>
+        <v>34.350179400000002</v>
+      </c>
+      <c r="N68">
+        <f t="shared" si="7"/>
+        <v>15.2081436</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A69">
         <v>0.22578799999999999</v>
       </c>
@@ -1172,8 +2691,30 @@
       <c r="C69">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G69">
+        <f t="shared" si="4"/>
+        <v>46.263961199999997</v>
+      </c>
+      <c r="H69">
+        <f t="shared" si="5"/>
+        <v>21.386847299999999</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <f t="shared" si="6"/>
+        <v>32.377999199999998</v>
+      </c>
+      <c r="N69">
+        <f t="shared" si="7"/>
+        <v>14.9676618</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A70">
         <v>0.21232500000000001</v>
       </c>
@@ -1183,8 +2724,30 @@
       <c r="C70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G70">
+        <f t="shared" si="4"/>
+        <v>43.505392500000006</v>
+      </c>
+      <c r="H70">
+        <f t="shared" si="5"/>
+        <v>21.007372500000002</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <f t="shared" si="6"/>
+        <v>30.447405000000003</v>
+      </c>
+      <c r="N70">
+        <f t="shared" si="7"/>
+        <v>14.702085000000002</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A71">
         <v>0.19916700000000001</v>
       </c>
@@ -1194,8 +2757,30 @@
       <c r="C71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G71">
+        <f t="shared" si="4"/>
+        <v>40.809318300000001</v>
+      </c>
+      <c r="H71">
+        <f t="shared" si="5"/>
+        <v>20.592859799999999</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <f t="shared" si="6"/>
+        <v>28.560547800000002</v>
+      </c>
+      <c r="N71">
+        <f t="shared" si="7"/>
+        <v>14.411986799999999</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A72">
         <v>0.18633</v>
       </c>
@@ -1205,8 +2790,30 @@
       <c r="C72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G72">
+        <f t="shared" si="4"/>
+        <v>38.179017000000002</v>
+      </c>
+      <c r="H72">
+        <f t="shared" si="5"/>
+        <v>20.144948400000001</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <f t="shared" si="6"/>
+        <v>26.719722000000001</v>
+      </c>
+      <c r="N72">
+        <f t="shared" si="7"/>
+        <v>14.098514400000001</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A73">
         <v>0.17382600000000001</v>
       </c>
@@ -1216,8 +2823,30 @@
       <c r="C73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G73">
+        <f t="shared" si="4"/>
+        <v>35.616947400000001</v>
+      </c>
+      <c r="H73">
+        <f t="shared" si="5"/>
+        <v>19.664662800000002</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <f t="shared" si="6"/>
+        <v>24.926648400000001</v>
+      </c>
+      <c r="N73">
+        <f t="shared" si="7"/>
+        <v>13.762384800000001</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A74">
         <v>0.16167000000000001</v>
       </c>
@@ -1227,8 +2856,30 @@
       <c r="C74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G74">
+        <f t="shared" si="4"/>
+        <v>33.126183000000005</v>
+      </c>
+      <c r="H74">
+        <f t="shared" si="5"/>
+        <v>19.1534373</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <f t="shared" si="6"/>
+        <v>23.183478000000001</v>
+      </c>
+      <c r="N74">
+        <f t="shared" si="7"/>
+        <v>13.404601800000002</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A75">
         <v>0.14987600000000001</v>
       </c>
@@ -1238,8 +2889,30 @@
       <c r="C75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G75">
+        <f t="shared" si="4"/>
+        <v>30.709592400000002</v>
+      </c>
+      <c r="H75">
+        <f t="shared" si="5"/>
+        <v>18.612911100000002</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <f t="shared" si="6"/>
+        <v>21.492218400000002</v>
+      </c>
+      <c r="N75">
+        <f t="shared" si="7"/>
+        <v>13.026312600000001</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A76">
         <v>0.138456</v>
       </c>
@@ -1249,8 +2922,30 @@
       <c r="C76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G76">
+        <f t="shared" si="4"/>
+        <v>28.369634399999999</v>
+      </c>
+      <c r="H76">
+        <f t="shared" si="5"/>
+        <v>18.044723400000002</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <f t="shared" si="6"/>
+        <v>19.854590399999999</v>
+      </c>
+      <c r="N76">
+        <f t="shared" si="7"/>
+        <v>12.628664400000002</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A77">
         <v>0.12742300000000001</v>
       </c>
@@ -1260,8 +2955,30 @@
       <c r="C77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G77">
+        <f t="shared" si="4"/>
+        <v>26.108972700000002</v>
+      </c>
+      <c r="H77">
+        <f t="shared" si="5"/>
+        <v>17.450308500000002</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <f t="shared" si="6"/>
+        <v>18.272458200000003</v>
+      </c>
+      <c r="N77">
+        <f t="shared" si="7"/>
+        <v>12.212661000000001</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A78">
         <v>0.116788</v>
       </c>
@@ -1271,8 +2988,30 @@
       <c r="C78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G78">
+        <f t="shared" si="4"/>
+        <v>23.929861200000001</v>
+      </c>
+      <c r="H78">
+        <f t="shared" si="5"/>
+        <v>16.8317154</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <f t="shared" si="6"/>
+        <v>16.7473992</v>
+      </c>
+      <c r="N78">
+        <f t="shared" si="7"/>
+        <v>11.779736400000001</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A79">
         <v>0.106562</v>
       </c>
@@ -1282,8 +3021,30 @@
       <c r="C79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G79">
+        <f t="shared" si="4"/>
+        <v>21.834553800000002</v>
+      </c>
+      <c r="H79">
+        <f t="shared" si="5"/>
+        <v>16.1905833</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <f t="shared" si="6"/>
+        <v>15.280990800000001</v>
+      </c>
+      <c r="N79">
+        <f t="shared" si="7"/>
+        <v>11.331037800000001</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A80">
         <v>9.6754999999999994E-2</v>
       </c>
@@ -1293,8 +3054,30 @@
       <c r="C80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G80">
+        <f t="shared" si="4"/>
+        <v>19.8250995</v>
+      </c>
+      <c r="H80">
+        <f t="shared" si="5"/>
+        <v>15.5287563</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <f t="shared" si="6"/>
+        <v>13.874667000000001</v>
+      </c>
+      <c r="N80">
+        <f t="shared" si="7"/>
+        <v>10.867855799999999</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A81">
         <v>8.7378999999999998E-2</v>
       </c>
@@ -1304,8 +3087,30 @@
       <c r="C81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G81">
+        <f t="shared" si="4"/>
+        <v>17.9039571</v>
+      </c>
+      <c r="H81">
+        <f t="shared" si="5"/>
+        <v>14.848078500000002</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <f t="shared" si="6"/>
+        <v>12.5301486</v>
+      </c>
+      <c r="N81">
+        <f t="shared" si="7"/>
+        <v>10.391481000000001</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A82">
         <v>7.8441999999999998E-2</v>
       </c>
@@ -1315,8 +3120,30 @@
       <c r="C82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G82">
+        <f t="shared" si="4"/>
+        <v>16.072765799999999</v>
+      </c>
+      <c r="H82">
+        <f t="shared" si="5"/>
+        <v>14.150394</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <f t="shared" si="6"/>
+        <v>11.248582799999999</v>
+      </c>
+      <c r="N82">
+        <f t="shared" si="7"/>
+        <v>9.9032040000000006</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A83">
         <v>6.9952E-2</v>
       </c>
@@ -1326,8 +3153,30 @@
       <c r="C83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G83">
+        <f t="shared" si="4"/>
+        <v>14.3331648</v>
+      </c>
+      <c r="H83">
+        <f t="shared" si="5"/>
+        <v>13.437956700000001</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <f t="shared" si="6"/>
+        <v>10.031116800000001</v>
+      </c>
+      <c r="N83">
+        <f t="shared" si="7"/>
+        <v>9.4046022000000011</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A84">
         <v>6.1918000000000001E-2</v>
       </c>
@@ -1337,8 +3186,30 @@
       <c r="C84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G84">
+        <f t="shared" si="4"/>
+        <v>12.6869982</v>
+      </c>
+      <c r="H84">
+        <f t="shared" si="5"/>
+        <v>12.712200900000001</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <f t="shared" si="6"/>
+        <v>8.8790411999999996</v>
+      </c>
+      <c r="N84">
+        <f t="shared" si="7"/>
+        <v>8.8966794</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A85">
         <v>5.4348E-2</v>
       </c>
@@ -1348,8 +3219,30 @@
       <c r="C85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G85">
+        <f t="shared" si="4"/>
+        <v>11.1359052</v>
+      </c>
+      <c r="H85">
+        <f t="shared" si="5"/>
+        <v>11.9753805</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <f t="shared" si="6"/>
+        <v>7.7935032</v>
+      </c>
+      <c r="N85">
+        <f t="shared" si="7"/>
+        <v>8.3810129999999994</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A86">
         <v>4.7246999999999997E-2</v>
       </c>
@@ -1359,8 +3252,30 @@
       <c r="C86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G86">
+        <f t="shared" si="4"/>
+        <v>9.680910299999999</v>
+      </c>
+      <c r="H86">
+        <f t="shared" si="5"/>
+        <v>11.229339599999999</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <f t="shared" si="6"/>
+        <v>6.7752197999999995</v>
+      </c>
+      <c r="N86">
+        <f t="shared" si="7"/>
+        <v>7.8588936</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A87">
         <v>4.0622999999999999E-2</v>
       </c>
@@ -1370,8 +3285,30 @@
       <c r="C87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G87">
+        <f t="shared" si="4"/>
+        <v>8.3236527000000002</v>
+      </c>
+      <c r="H87">
+        <f t="shared" si="5"/>
+        <v>10.475922300000001</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <f t="shared" si="6"/>
+        <v>5.8253382</v>
+      </c>
+      <c r="N87">
+        <f t="shared" si="7"/>
+        <v>7.3316118000000001</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A88">
         <v>3.4480999999999998E-2</v>
       </c>
@@ -1381,8 +3318,30 @@
       <c r="C88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G88">
+        <f t="shared" si="4"/>
+        <v>7.0651568999999999</v>
+      </c>
+      <c r="H88">
+        <f t="shared" si="5"/>
+        <v>9.7167677999999995</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <f t="shared" si="6"/>
+        <v>4.9445753999999997</v>
+      </c>
+      <c r="N88">
+        <f t="shared" si="7"/>
+        <v>6.8003147999999998</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A89">
         <v>2.8826000000000001E-2</v>
       </c>
@@ -1392,8 +3351,30 @@
       <c r="C89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G89">
+        <f t="shared" si="4"/>
+        <v>5.9064474000000002</v>
+      </c>
+      <c r="H89">
+        <f t="shared" si="5"/>
+        <v>8.9537202000000011</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <f t="shared" si="6"/>
+        <v>4.1336484000000002</v>
+      </c>
+      <c r="N89">
+        <f t="shared" si="7"/>
+        <v>6.2662932000000007</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A90">
         <v>2.3663E-2</v>
       </c>
@@ -1403,8 +3384,30 @@
       <c r="C90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G90">
+        <f t="shared" si="4"/>
+        <v>4.8485487000000003</v>
+      </c>
+      <c r="H90">
+        <f t="shared" si="5"/>
+        <v>8.1884186999999997</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <f t="shared" si="6"/>
+        <v>3.3932742</v>
+      </c>
+      <c r="N90">
+        <f t="shared" si="7"/>
+        <v>5.7306942000000003</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A91">
         <v>1.8994E-2</v>
       </c>
@@ -1414,8 +3417,30 @@
       <c r="C91">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G91">
+        <f t="shared" si="4"/>
+        <v>3.8918706000000003</v>
+      </c>
+      <c r="H91">
+        <f t="shared" si="5"/>
+        <v>7.4225025000000002</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <f t="shared" si="6"/>
+        <v>2.7237396</v>
+      </c>
+      <c r="N91">
+        <f t="shared" si="7"/>
+        <v>5.1946650000000005</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A92">
         <v>1.4825E-2</v>
       </c>
@@ -1425,8 +3450,30 @@
       <c r="C92">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G92">
+        <f t="shared" si="4"/>
+        <v>3.0376425</v>
+      </c>
+      <c r="H92">
+        <f t="shared" si="5"/>
+        <v>6.6576108000000005</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <f t="shared" si="6"/>
+        <v>2.1259049999999999</v>
+      </c>
+      <c r="N92">
+        <f t="shared" si="7"/>
+        <v>4.6593528000000006</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A93">
         <v>1.1155999999999999E-2</v>
       </c>
@@ -1436,8 +3483,30 @@
       <c r="C93">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G93">
+        <f t="shared" si="4"/>
+        <v>2.2858643999999999</v>
+      </c>
+      <c r="H93">
+        <f t="shared" si="5"/>
+        <v>5.8947681000000003</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <f t="shared" si="6"/>
+        <v>1.5997703999999999</v>
+      </c>
+      <c r="N93">
+        <f t="shared" si="7"/>
+        <v>4.1254746000000004</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A94">
         <v>7.9909999999999998E-3</v>
       </c>
@@ -1447,8 +3516,30 @@
       <c r="C94">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G94">
+        <f t="shared" si="4"/>
+        <v>1.6373559</v>
+      </c>
+      <c r="H94">
+        <f t="shared" si="5"/>
+        <v>5.1354087000000002</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <f t="shared" si="6"/>
+        <v>1.1459094000000001</v>
+      </c>
+      <c r="N94">
+        <f t="shared" si="7"/>
+        <v>3.5940341999999998</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A95">
         <v>5.3309999999999998E-3</v>
       </c>
@@ -1458,8 +3549,30 @@
       <c r="C95">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G95">
+        <f t="shared" si="4"/>
+        <v>1.0923219</v>
+      </c>
+      <c r="H95">
+        <f t="shared" si="5"/>
+        <v>4.3809669000000007</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <f t="shared" si="6"/>
+        <v>0.76446539999999996</v>
+      </c>
+      <c r="N95">
+        <f t="shared" si="7"/>
+        <v>3.0660354000000001</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A96">
         <v>3.1770000000000001E-3</v>
       </c>
@@ -1469,8 +3582,30 @@
       <c r="C96">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G96">
+        <f t="shared" si="4"/>
+        <v>0.65096730000000003</v>
+      </c>
+      <c r="H96">
+        <f t="shared" si="5"/>
+        <v>3.6320573999999999</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <f t="shared" si="6"/>
+        <v>0.45558180000000004</v>
+      </c>
+      <c r="N96">
+        <f t="shared" si="7"/>
+        <v>2.5419084000000001</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A97">
         <v>1.5299999999999999E-3</v>
       </c>
@@ -1480,8 +3615,30 @@
       <c r="C97">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G97">
+        <f t="shared" si="4"/>
+        <v>0.31349699999999997</v>
+      </c>
+      <c r="H97">
+        <f t="shared" si="5"/>
+        <v>2.8897046999999998</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <f t="shared" si="6"/>
+        <v>0.21940199999999999</v>
+      </c>
+      <c r="N97">
+        <f t="shared" si="7"/>
+        <v>2.0223702000000001</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A98">
         <v>3.8900000000000002E-4</v>
       </c>
@@ -1491,8 +3648,30 @@
       <c r="C98">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G98">
+        <f t="shared" si="4"/>
+        <v>7.9706100000000002E-2</v>
+      </c>
+      <c r="H98">
+        <f t="shared" si="5"/>
+        <v>2.1549333000000002</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <f t="shared" si="6"/>
+        <v>5.5782600000000009E-2</v>
+      </c>
+      <c r="N98">
+        <f t="shared" si="7"/>
+        <v>1.5081378000000001</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A99">
         <v>-2.4499999999999999E-4</v>
       </c>
@@ -1502,8 +3681,30 @@
       <c r="C99">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G99">
+        <f t="shared" si="4"/>
+        <v>-5.0200500000000002E-2</v>
+      </c>
+      <c r="H99">
+        <f t="shared" si="5"/>
+        <v>1.4279481000000001</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <f t="shared" si="6"/>
+        <v>-3.5132999999999998E-2</v>
+      </c>
+      <c r="N99">
+        <f t="shared" si="7"/>
+        <v>0.99935460000000009</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A100">
         <v>-3.7399999999999998E-4</v>
       </c>
@@ -1513,8 +3714,30 @@
       <c r="C100">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G100">
+        <f t="shared" si="4"/>
+        <v>-7.6632599999999995E-2</v>
+      </c>
+      <c r="H100">
+        <f t="shared" si="5"/>
+        <v>0.70956870000000005</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="M100">
+        <f t="shared" si="6"/>
+        <v>-5.3631600000000001E-2</v>
+      </c>
+      <c r="N100">
+        <f t="shared" si="7"/>
+        <v>0.49659419999999999</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A101">
         <v>0</v>
       </c>
@@ -1524,8 +3747,30 @@
       <c r="C101">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G101">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A102">
         <v>8.6799999999999996E-4</v>
       </c>
@@ -1535,8 +3780,30 @@
       <c r="C102">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G102">
+        <f t="shared" si="4"/>
+        <v>0.17785319999999999</v>
+      </c>
+      <c r="H102">
+        <f t="shared" si="5"/>
+        <v>-0.69112770000000001</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <f t="shared" si="6"/>
+        <v>0.1244712</v>
+      </c>
+      <c r="N102">
+        <f t="shared" si="7"/>
+        <v>-0.48368820000000001</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A103">
         <v>2.2179999999999999E-3</v>
       </c>
@@ -1546,8 +3813,30 @@
       <c r="C103">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G103">
+        <f t="shared" si="4"/>
+        <v>0.45446819999999999</v>
+      </c>
+      <c r="H103">
+        <f t="shared" si="5"/>
+        <v>-1.3545939</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <f t="shared" si="6"/>
+        <v>0.31806119999999999</v>
+      </c>
+      <c r="N103">
+        <f t="shared" si="7"/>
+        <v>-0.94801740000000001</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A104">
         <v>4.0489999999999996E-3</v>
       </c>
@@ -1557,8 +3846,30 @@
       <c r="C104">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G104">
+        <f t="shared" si="4"/>
+        <v>0.82964009999999999</v>
+      </c>
+      <c r="H104">
+        <f t="shared" si="5"/>
+        <v>-1.9899888000000001</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <f t="shared" si="6"/>
+        <v>0.58062659999999999</v>
+      </c>
+      <c r="N104">
+        <f t="shared" si="7"/>
+        <v>-1.3927008000000001</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A105">
         <v>6.3550000000000004E-3</v>
       </c>
@@ -1568,8 +3879,30 @@
       <c r="C105">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G105">
+        <f t="shared" si="4"/>
+        <v>1.3021395000000002</v>
+      </c>
+      <c r="H105">
+        <f t="shared" si="5"/>
+        <v>-2.5973123999999999</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <f t="shared" si="6"/>
+        <v>0.91130700000000009</v>
+      </c>
+      <c r="N105">
+        <f t="shared" si="7"/>
+        <v>-1.8177384000000001</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A106">
         <v>9.1339999999999998E-3</v>
       </c>
@@ -1579,8 +3912,30 @@
       <c r="C106">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G106">
+        <f t="shared" si="4"/>
+        <v>1.8715565999999999</v>
+      </c>
+      <c r="H106">
+        <f t="shared" si="5"/>
+        <v>-3.1765647000000001</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <f t="shared" si="6"/>
+        <v>1.3098156000000001</v>
+      </c>
+      <c r="N106">
+        <f t="shared" si="7"/>
+        <v>-2.2231301999999999</v>
+      </c>
+      <c r="O106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A107">
         <v>1.2382000000000001E-2</v>
       </c>
@@ -1590,8 +3945,30 @@
       <c r="C107">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G107">
+        <f t="shared" si="4"/>
+        <v>2.5370718000000001</v>
+      </c>
+      <c r="H107">
+        <f t="shared" si="5"/>
+        <v>-3.7275407999999999</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <f t="shared" si="6"/>
+        <v>1.7755788000000001</v>
+      </c>
+      <c r="N107">
+        <f t="shared" si="7"/>
+        <v>-2.6087328000000003</v>
+      </c>
+      <c r="O107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A108">
         <v>1.6091999999999999E-2</v>
       </c>
@@ -1601,8 +3978,30 @@
       <c r="C108">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G108">
+        <f t="shared" si="4"/>
+        <v>3.2972508</v>
+      </c>
+      <c r="H108">
+        <f t="shared" si="5"/>
+        <v>-4.2504455999999999</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <f t="shared" si="6"/>
+        <v>2.3075928000000001</v>
+      </c>
+      <c r="N108">
+        <f t="shared" si="7"/>
+        <v>-2.9746896</v>
+      </c>
+      <c r="O108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A109">
         <v>2.0261000000000001E-2</v>
       </c>
@@ -1612,8 +4011,30 @@
       <c r="C109">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G109">
+        <f t="shared" si="4"/>
+        <v>4.1514789000000007</v>
+      </c>
+      <c r="H109">
+        <f t="shared" si="5"/>
+        <v>-4.7452791000000003</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <f t="shared" si="6"/>
+        <v>2.9054274000000002</v>
+      </c>
+      <c r="N109">
+        <f t="shared" si="7"/>
+        <v>-3.3210006000000001</v>
+      </c>
+      <c r="O109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A110">
         <v>2.4882000000000001E-2</v>
       </c>
@@ -1623,8 +4044,30 @@
       <c r="C110">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G110">
+        <f t="shared" si="4"/>
+        <v>5.0983218000000008</v>
+      </c>
+      <c r="H110">
+        <f t="shared" si="5"/>
+        <v>-5.2116315000000002</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <f t="shared" si="6"/>
+        <v>3.5680788000000003</v>
+      </c>
+      <c r="N110">
+        <f t="shared" si="7"/>
+        <v>-3.6473789999999999</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A111">
         <v>2.9949E-2</v>
       </c>
@@ -1634,8 +4077,30 @@
       <c r="C111">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G111">
+        <f t="shared" si="4"/>
+        <v>6.1365501</v>
+      </c>
+      <c r="H111">
+        <f t="shared" si="5"/>
+        <v>-5.6499126000000004</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <f t="shared" si="6"/>
+        <v>4.2946866000000004</v>
+      </c>
+      <c r="N111">
+        <f t="shared" si="7"/>
+        <v>-3.9541116000000005</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A112">
         <v>3.5457000000000002E-2</v>
       </c>
@@ -1645,8 +4110,30 @@
       <c r="C112">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G112">
+        <f t="shared" si="4"/>
+        <v>7.2651393000000004</v>
+      </c>
+      <c r="H112">
+        <f t="shared" si="5"/>
+        <v>-6.0599175000000001</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <f t="shared" si="6"/>
+        <v>5.0845338000000009</v>
+      </c>
+      <c r="N112">
+        <f t="shared" si="7"/>
+        <v>-4.2410550000000002</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A113">
         <v>4.1397000000000003E-2</v>
       </c>
@@ -1656,8 +4143,30 @@
       <c r="C113">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G113">
+        <f t="shared" si="4"/>
+        <v>8.4822453000000007</v>
+      </c>
+      <c r="H113">
+        <f t="shared" si="5"/>
+        <v>-6.4420560000000009</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="M113">
+        <f t="shared" si="6"/>
+        <v>5.9363298000000011</v>
+      </c>
+      <c r="N113">
+        <f t="shared" si="7"/>
+        <v>-4.5084960000000009</v>
+      </c>
+      <c r="O113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A114">
         <v>4.7764000000000001E-2</v>
       </c>
@@ -1667,8 +4176,30 @@
       <c r="C114">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G114">
+        <f t="shared" si="4"/>
+        <v>9.786843600000001</v>
+      </c>
+      <c r="H114">
+        <f t="shared" si="5"/>
+        <v>-6.7959183000000003</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <f t="shared" si="6"/>
+        <v>6.8493576000000003</v>
+      </c>
+      <c r="N114">
+        <f t="shared" si="7"/>
+        <v>-4.7561478000000008</v>
+      </c>
+      <c r="O114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A115">
         <v>5.4550000000000001E-2</v>
       </c>
@@ -1678,8 +4209,30 @@
       <c r="C115">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G115">
+        <f t="shared" si="4"/>
+        <v>11.177295000000001</v>
+      </c>
+      <c r="H115">
+        <f t="shared" si="5"/>
+        <v>-7.1219142</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <f t="shared" si="6"/>
+        <v>7.8224700000000009</v>
+      </c>
+      <c r="N115">
+        <f t="shared" si="7"/>
+        <v>-4.9842971999999994</v>
+      </c>
+      <c r="O115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A116">
         <v>6.1746000000000002E-2</v>
       </c>
@@ -1689,8 +4242,30 @@
       <c r="C116">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G116">
+        <f t="shared" si="4"/>
+        <v>12.651755400000001</v>
+      </c>
+      <c r="H116">
+        <f t="shared" si="5"/>
+        <v>-7.4202486000000007</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <f t="shared" si="6"/>
+        <v>8.8543764000000014</v>
+      </c>
+      <c r="N116">
+        <f t="shared" si="7"/>
+        <v>-5.193087600000001</v>
+      </c>
+      <c r="O116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A117">
         <v>6.9346000000000005E-2</v>
       </c>
@@ -1700,8 +4275,30 @@
       <c r="C117">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G117">
+        <f t="shared" si="4"/>
+        <v>14.208995400000001</v>
+      </c>
+      <c r="H117">
+        <f t="shared" si="5"/>
+        <v>-7.6911263999999999</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <f t="shared" si="6"/>
+        <v>9.944216400000002</v>
+      </c>
+      <c r="N117">
+        <f t="shared" si="7"/>
+        <v>-5.3826624000000001</v>
+      </c>
+      <c r="O117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A118">
         <v>7.7340000000000006E-2</v>
       </c>
@@ -1711,8 +4308,30 @@
       <c r="C118">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G118">
+        <f t="shared" si="4"/>
+        <v>15.846966000000002</v>
+      </c>
+      <c r="H118">
+        <f t="shared" si="5"/>
+        <v>-7.934752500000001</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <f t="shared" si="6"/>
+        <v>11.090556000000001</v>
+      </c>
+      <c r="N118">
+        <f t="shared" si="7"/>
+        <v>-5.5531650000000008</v>
+      </c>
+      <c r="O118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A119">
         <v>8.5720000000000005E-2</v>
       </c>
@@ -1722,8 +4341,30 @@
       <c r="C119">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G119">
+        <f t="shared" si="4"/>
+        <v>17.564028</v>
+      </c>
+      <c r="H119">
+        <f t="shared" si="5"/>
+        <v>-8.1513317999999995</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <f t="shared" si="6"/>
+        <v>12.292248000000001</v>
+      </c>
+      <c r="N119">
+        <f t="shared" si="7"/>
+        <v>-5.7047388000000003</v>
+      </c>
+      <c r="O119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A120">
         <v>9.4478000000000006E-2</v>
       </c>
@@ -1733,8 +4374,30 @@
       <c r="C120">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G120">
+        <f t="shared" si="4"/>
+        <v>19.358542200000002</v>
+      </c>
+      <c r="H120">
+        <f t="shared" si="5"/>
+        <v>-8.3412741000000015</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <f t="shared" si="6"/>
+        <v>13.548145200000002</v>
+      </c>
+      <c r="N120">
+        <f t="shared" si="7"/>
+        <v>-5.8376706000000009</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A121">
         <v>0.103604</v>
       </c>
@@ -1744,8 +4407,30 @@
       <c r="C121">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G121">
+        <f t="shared" si="4"/>
+        <v>21.228459600000001</v>
+      </c>
+      <c r="H121">
+        <f t="shared" si="5"/>
+        <v>-8.5049892000000007</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="M121">
+        <f t="shared" si="6"/>
+        <v>14.856813600000001</v>
+      </c>
+      <c r="N121">
+        <f t="shared" si="7"/>
+        <v>-5.9522472000000004</v>
+      </c>
+      <c r="O121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A122">
         <v>0.11309</v>
       </c>
@@ -1755,8 +4440,30 @@
       <c r="C122">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G122">
+        <f t="shared" si="4"/>
+        <v>23.172141</v>
+      </c>
+      <c r="H122">
+        <f t="shared" si="5"/>
+        <v>-8.6430918000000005</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <f t="shared" si="6"/>
+        <v>16.217106000000001</v>
+      </c>
+      <c r="N122">
+        <f t="shared" si="7"/>
+        <v>-6.0488987999999999</v>
+      </c>
+      <c r="O122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A123">
         <v>0.12292500000000001</v>
       </c>
@@ -1766,8 +4473,30 @@
       <c r="C123">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G123">
+        <f t="shared" si="4"/>
+        <v>25.187332500000004</v>
+      </c>
+      <c r="H123">
+        <f t="shared" si="5"/>
+        <v>-8.7557867999999992</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <f t="shared" si="6"/>
+        <v>17.627445000000002</v>
+      </c>
+      <c r="N123">
+        <f t="shared" si="7"/>
+        <v>-6.1277688000000001</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A124">
         <v>0.133101</v>
       </c>
@@ -1777,8 +4506,30 @@
       <c r="C124">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G124">
+        <f t="shared" si="4"/>
+        <v>27.272394900000002</v>
+      </c>
+      <c r="H124">
+        <f t="shared" si="5"/>
+        <v>-8.8440987</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <f t="shared" si="6"/>
+        <v>19.086683400000002</v>
+      </c>
+      <c r="N124">
+        <f t="shared" si="7"/>
+        <v>-6.1895742</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A125">
         <v>0.14360800000000001</v>
       </c>
@@ -1788,8 +4539,30 @@
       <c r="C125">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G125">
+        <f t="shared" si="4"/>
+        <v>29.425279200000002</v>
+      </c>
+      <c r="H125">
+        <f t="shared" si="5"/>
+        <v>-8.908232400000001</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <f t="shared" si="6"/>
+        <v>20.593387200000002</v>
+      </c>
+      <c r="N125">
+        <f t="shared" si="7"/>
+        <v>-6.2344584000000003</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A126">
         <v>0.15443699999999999</v>
       </c>
@@ -1799,8 +4572,30 @@
       <c r="C126">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G126">
+        <f t="shared" si="4"/>
+        <v>31.644141299999998</v>
+      </c>
+      <c r="H126">
+        <f t="shared" si="5"/>
+        <v>-8.9490075000000004</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <f t="shared" si="6"/>
+        <v>22.146265799999998</v>
+      </c>
+      <c r="N126">
+        <f t="shared" si="7"/>
+        <v>-6.2629950000000001</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A127">
         <v>0.165577</v>
       </c>
@@ -1810,8 +4605,30 @@
       <c r="C127">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G127">
+        <f t="shared" si="4"/>
+        <v>33.926727300000003</v>
+      </c>
+      <c r="H127">
+        <f t="shared" si="5"/>
+        <v>-8.9672435999999998</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <f t="shared" si="6"/>
+        <v>23.743741800000002</v>
+      </c>
+      <c r="N127">
+        <f t="shared" si="7"/>
+        <v>-6.2757575999999995</v>
+      </c>
+      <c r="O127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A128">
         <v>0.17701800000000001</v>
       </c>
@@ -1821,8 +4638,30 @@
       <c r="C128">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G128">
+        <f t="shared" si="4"/>
+        <v>36.270988200000005</v>
+      </c>
+      <c r="H128">
+        <f t="shared" si="5"/>
+        <v>-8.9639652000000005</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <f t="shared" si="6"/>
+        <v>25.384381200000004</v>
+      </c>
+      <c r="N128">
+        <f t="shared" si="7"/>
+        <v>-6.2734632000000001</v>
+      </c>
+      <c r="O128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A129">
         <v>0.18875</v>
       </c>
@@ -1832,8 +4671,30 @@
       <c r="C129">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G129">
+        <f t="shared" si="4"/>
+        <v>38.674875</v>
+      </c>
+      <c r="H129">
+        <f t="shared" si="5"/>
+        <v>-8.9397870000000008</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+      <c r="M129">
+        <f t="shared" si="6"/>
+        <v>27.066750000000003</v>
+      </c>
+      <c r="N129">
+        <f t="shared" si="7"/>
+        <v>-6.2565420000000005</v>
+      </c>
+      <c r="O129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A130">
         <v>0.200763</v>
       </c>
@@ -1843,8 +4704,30 @@
       <c r="C130">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G130">
+        <f t="shared" ref="G130:G193" si="8">$F$1*$A130</f>
+        <v>41.136338700000003</v>
+      </c>
+      <c r="H130">
+        <f t="shared" ref="H130:H193" si="9">$F$1*$B130</f>
+        <v>-8.8957335000000004</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <f t="shared" ref="M130:M193" si="10">$L$1*$A130</f>
+        <v>28.7894142</v>
+      </c>
+      <c r="N130">
+        <f t="shared" ref="N130:N193" si="11">$L$1*$B130</f>
+        <v>-6.2257110000000004</v>
+      </c>
+      <c r="O130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A131">
         <v>0.21304699999999999</v>
       </c>
@@ -1854,8 +4737,30 @@
       <c r="C131">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G131">
+        <f t="shared" si="8"/>
+        <v>43.6533303</v>
+      </c>
+      <c r="H131">
+        <f t="shared" si="9"/>
+        <v>-8.8328292000000008</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="M131">
+        <f t="shared" si="10"/>
+        <v>30.550939799999998</v>
+      </c>
+      <c r="N131">
+        <f t="shared" si="11"/>
+        <v>-6.1816872000000007</v>
+      </c>
+      <c r="O131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A132">
         <v>0.22559100000000001</v>
       </c>
@@ -1865,8 +4770,30 @@
       <c r="C132">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G132">
+        <f t="shared" si="8"/>
+        <v>46.223595900000007</v>
+      </c>
+      <c r="H132">
+        <f t="shared" si="9"/>
+        <v>-8.7523035</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <f t="shared" si="10"/>
+        <v>32.3497494</v>
+      </c>
+      <c r="N132">
+        <f t="shared" si="11"/>
+        <v>-6.125331000000001</v>
+      </c>
+      <c r="O132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A133">
         <v>0.23838500000000001</v>
       </c>
@@ -1876,8 +4803,30 @@
       <c r="C133">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G133">
+        <f t="shared" si="8"/>
+        <v>48.845086500000001</v>
+      </c>
+      <c r="H133">
+        <f t="shared" si="9"/>
+        <v>-8.6549759999999996</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <f t="shared" si="10"/>
+        <v>34.184409000000002</v>
+      </c>
+      <c r="N133">
+        <f t="shared" si="11"/>
+        <v>-6.0572160000000004</v>
+      </c>
+      <c r="O133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A134">
         <v>0.251417</v>
       </c>
@@ -1887,8 +4836,30 @@
       <c r="C134">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G134">
+        <f t="shared" si="8"/>
+        <v>51.515343300000005</v>
+      </c>
+      <c r="H134">
+        <f t="shared" si="9"/>
+        <v>-8.5420760999999992</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <f t="shared" si="10"/>
+        <v>36.0531978</v>
+      </c>
+      <c r="N134">
+        <f t="shared" si="11"/>
+        <v>-5.9782025999999995</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A135">
         <v>0.264677</v>
       </c>
@@ -1898,8 +4869,30 @@
       <c r="C135">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G135">
+        <f t="shared" si="8"/>
+        <v>54.232317299999998</v>
+      </c>
+      <c r="H135">
+        <f t="shared" si="9"/>
+        <v>-8.4150381000000003</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <f t="shared" si="10"/>
+        <v>37.954681800000003</v>
+      </c>
+      <c r="N135">
+        <f t="shared" si="11"/>
+        <v>-5.8892946000000004</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A136">
         <v>0.27815400000000001</v>
       </c>
@@ -1909,8 +4902,30 @@
       <c r="C136">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G136">
+        <f t="shared" si="8"/>
+        <v>56.993754600000003</v>
+      </c>
+      <c r="H136">
+        <f t="shared" si="9"/>
+        <v>-8.2750913999999991</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <f t="shared" si="10"/>
+        <v>39.887283600000004</v>
+      </c>
+      <c r="N136">
+        <f t="shared" si="11"/>
+        <v>-5.7913524000000001</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A137">
         <v>0.29183700000000001</v>
       </c>
@@ -1920,8 +4935,30 @@
       <c r="C137">
         <v>0</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G137">
+        <f t="shared" si="8"/>
+        <v>59.797401300000004</v>
+      </c>
+      <c r="H137">
+        <f t="shared" si="9"/>
+        <v>-8.1232605000000007</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <f t="shared" si="10"/>
+        <v>41.849425800000006</v>
+      </c>
+      <c r="N137">
+        <f t="shared" si="11"/>
+        <v>-5.6850930000000002</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A138">
         <v>0.30571399999999999</v>
       </c>
@@ -1931,8 +4968,30 @@
       <c r="C138">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G138">
+        <f t="shared" si="8"/>
+        <v>62.640798599999997</v>
+      </c>
+      <c r="H138">
+        <f t="shared" si="9"/>
+        <v>-7.9609797000000002</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <f t="shared" si="10"/>
+        <v>43.839387600000002</v>
+      </c>
+      <c r="N138">
+        <f t="shared" si="11"/>
+        <v>-5.5715202000000001</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A139">
         <v>0.319774</v>
       </c>
@@ -1942,8 +5001,30 @@
       <c r="C139">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G139">
+        <f t="shared" si="8"/>
+        <v>65.521692600000009</v>
+      </c>
+      <c r="H139">
+        <f t="shared" si="9"/>
+        <v>-7.7894784000000001</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <f t="shared" si="10"/>
+        <v>45.855591600000004</v>
+      </c>
+      <c r="N139">
+        <f t="shared" si="11"/>
+        <v>-5.4514944000000005</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A140">
         <v>0.33400600000000003</v>
       </c>
@@ -1953,8 +5034,30 @@
       <c r="C140">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G140">
+        <f t="shared" si="8"/>
+        <v>68.437829400000012</v>
+      </c>
+      <c r="H140">
+        <f t="shared" si="9"/>
+        <v>-7.6101909000000001</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <f t="shared" si="10"/>
+        <v>47.896460400000002</v>
+      </c>
+      <c r="N140">
+        <f t="shared" si="11"/>
+        <v>-5.3260193999999998</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A141">
         <v>0.34839700000000001</v>
       </c>
@@ -1964,8 +5067,30 @@
       <c r="C141">
         <v>0</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G141">
+        <f t="shared" si="8"/>
+        <v>71.386545300000009</v>
+      </c>
+      <c r="H141">
+        <f t="shared" si="9"/>
+        <v>-7.4245515000000006</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="M141">
+        <f t="shared" si="10"/>
+        <v>49.960129800000004</v>
+      </c>
+      <c r="N141">
+        <f t="shared" si="11"/>
+        <v>-5.1960990000000002</v>
+      </c>
+      <c r="O141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A142">
         <v>0.36293500000000001</v>
       </c>
@@ -1975,8 +5100,30 @@
       <c r="C142">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G142">
+        <f t="shared" si="8"/>
+        <v>74.365381499999998</v>
+      </c>
+      <c r="H142">
+        <f t="shared" si="9"/>
+        <v>-7.2335847000000006</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="M142">
+        <f t="shared" si="10"/>
+        <v>52.044879000000002</v>
+      </c>
+      <c r="N142">
+        <f t="shared" si="11"/>
+        <v>-5.0624502000000007</v>
+      </c>
+      <c r="O142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A143">
         <v>0.37760899999999997</v>
       </c>
@@ -1986,8 +5133,30 @@
       <c r="C143">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G143">
+        <f t="shared" si="8"/>
+        <v>77.372084099999995</v>
+      </c>
+      <c r="H143">
+        <f t="shared" si="9"/>
+        <v>-7.0389297000000006</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <f t="shared" si="10"/>
+        <v>54.149130599999999</v>
+      </c>
+      <c r="N143">
+        <f t="shared" si="11"/>
+        <v>-4.9262202000000004</v>
+      </c>
+      <c r="O143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A144">
         <v>0.39240599999999998</v>
       </c>
@@ -1997,8 +5166,30 @@
       <c r="C144">
         <v>0</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G144">
+        <f t="shared" si="8"/>
+        <v>80.4039894</v>
+      </c>
+      <c r="H144">
+        <f t="shared" si="9"/>
+        <v>-6.8416110000000012</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <f t="shared" si="10"/>
+        <v>56.271020399999998</v>
+      </c>
+      <c r="N144">
+        <f t="shared" si="11"/>
+        <v>-4.788126000000001</v>
+      </c>
+      <c r="O144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A145">
         <v>0.40731400000000001</v>
       </c>
@@ -2008,8 +5199,30 @@
       <c r="C145">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G145">
+        <f t="shared" si="8"/>
+        <v>83.4586386</v>
+      </c>
+      <c r="H145">
+        <f t="shared" si="9"/>
+        <v>-6.6430628999999994</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <f t="shared" si="10"/>
+        <v>58.408827600000002</v>
+      </c>
+      <c r="N145">
+        <f t="shared" si="11"/>
+        <v>-4.6491714000000002</v>
+      </c>
+      <c r="O145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A146">
         <v>0.42231999999999997</v>
       </c>
@@ -2019,8 +5232,30 @@
       <c r="C146">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G146">
+        <f t="shared" si="8"/>
+        <v>86.533367999999996</v>
+      </c>
+      <c r="H146">
+        <f t="shared" si="9"/>
+        <v>-6.4445148000000003</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="M146">
+        <f t="shared" si="10"/>
+        <v>60.560687999999999</v>
+      </c>
+      <c r="N146">
+        <f t="shared" si="11"/>
+        <v>-4.5102168000000002</v>
+      </c>
+      <c r="O146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A147">
         <v>0.43741099999999999</v>
       </c>
@@ -2030,8 +5265,30 @@
       <c r="C147">
         <v>0</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G147">
+        <f t="shared" si="8"/>
+        <v>89.625513900000001</v>
+      </c>
+      <c r="H147">
+        <f t="shared" si="9"/>
+        <v>-6.2469912000000001</v>
+      </c>
+      <c r="I147">
+        <v>0</v>
+      </c>
+      <c r="M147">
+        <f t="shared" si="10"/>
+        <v>62.724737400000002</v>
+      </c>
+      <c r="N147">
+        <f t="shared" si="11"/>
+        <v>-4.3719792000000002</v>
+      </c>
+      <c r="O147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A148">
         <v>0.45271600000000001</v>
       </c>
@@ -2041,8 +5298,30 @@
       <c r="C148">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G148">
+        <f t="shared" si="8"/>
+        <v>92.761508400000011</v>
+      </c>
+      <c r="H148">
+        <f t="shared" si="9"/>
+        <v>-6.0494676000000007</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="M148">
+        <f t="shared" si="10"/>
+        <v>64.919474399999999</v>
+      </c>
+      <c r="N148">
+        <f t="shared" si="11"/>
+        <v>-4.2337416000000001</v>
+      </c>
+      <c r="O148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A149">
         <v>0.46810499999999999</v>
       </c>
@@ -2052,8 +5331,30 @@
       <c r="C149">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G149">
+        <f t="shared" si="8"/>
+        <v>95.914714500000002</v>
+      </c>
+      <c r="H149">
+        <f t="shared" si="9"/>
+        <v>-5.8476410999999997</v>
+      </c>
+      <c r="I149">
+        <v>0</v>
+      </c>
+      <c r="M149">
+        <f t="shared" si="10"/>
+        <v>67.126256999999995</v>
+      </c>
+      <c r="N149">
+        <f t="shared" si="11"/>
+        <v>-4.0924925999999999</v>
+      </c>
+      <c r="O149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A150">
         <v>0.48353400000000002</v>
       </c>
@@ -2063,8 +5364,30 @@
       <c r="C150">
         <v>0</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G150">
+        <f t="shared" si="8"/>
+        <v>99.076116600000006</v>
+      </c>
+      <c r="H150">
+        <f t="shared" si="9"/>
+        <v>-5.6427411000000003</v>
+      </c>
+      <c r="I150">
+        <v>0</v>
+      </c>
+      <c r="M150">
+        <f t="shared" si="10"/>
+        <v>69.338775600000005</v>
+      </c>
+      <c r="N150">
+        <f t="shared" si="11"/>
+        <v>-3.9490926000000002</v>
+      </c>
+      <c r="O150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A151">
         <v>0.49898900000000002</v>
       </c>
@@ -2074,8 +5397,30 @@
       <c r="C151">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G151">
+        <f t="shared" si="8"/>
+        <v>102.24284610000001</v>
+      </c>
+      <c r="H151">
+        <f t="shared" si="9"/>
+        <v>-5.4355871999999996</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+      <c r="M151">
+        <f t="shared" si="10"/>
+        <v>71.555022600000001</v>
+      </c>
+      <c r="N151">
+        <f t="shared" si="11"/>
+        <v>-3.8041152</v>
+      </c>
+      <c r="O151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A152">
         <v>0.51445399999999997</v>
       </c>
@@ -2085,8 +5430,30 @@
       <c r="C152">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G152">
+        <f t="shared" si="8"/>
+        <v>105.4116246</v>
+      </c>
+      <c r="H152">
+        <f t="shared" si="9"/>
+        <v>-5.2272039000000001</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+      <c r="M152">
+        <f t="shared" si="10"/>
+        <v>73.7727036</v>
+      </c>
+      <c r="N152">
+        <f t="shared" si="11"/>
+        <v>-3.6582773999999998</v>
+      </c>
+      <c r="O152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A153">
         <v>0.52991600000000005</v>
       </c>
@@ -2096,8 +5463,30 @@
       <c r="C153">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G153">
+        <f t="shared" si="8"/>
+        <v>108.57978840000001</v>
+      </c>
+      <c r="H153">
+        <f t="shared" si="9"/>
+        <v>-5.0182058999999999</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+      <c r="M153">
+        <f t="shared" si="10"/>
+        <v>75.989954400000016</v>
+      </c>
+      <c r="N153">
+        <f t="shared" si="11"/>
+        <v>-3.5120094000000002</v>
+      </c>
+      <c r="O153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A154">
         <v>0.54536099999999998</v>
       </c>
@@ -2107,8 +5496,30 @@
       <c r="C154">
         <v>0</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G154">
+        <f t="shared" si="8"/>
+        <v>111.7444689</v>
+      </c>
+      <c r="H154">
+        <f t="shared" si="9"/>
+        <v>-4.8094128000000005</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="M154">
+        <f t="shared" si="10"/>
+        <v>78.204767399999994</v>
+      </c>
+      <c r="N154">
+        <f t="shared" si="11"/>
+        <v>-3.3658847999999999</v>
+      </c>
+      <c r="O154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A155">
         <v>0.56077200000000005</v>
       </c>
@@ -2118,8 +5529,30 @@
       <c r="C155">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G155">
+        <f t="shared" si="8"/>
+        <v>114.90218280000002</v>
+      </c>
+      <c r="H155">
+        <f t="shared" si="9"/>
+        <v>-4.6016442</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="M155">
+        <f t="shared" si="10"/>
+        <v>80.41470480000001</v>
+      </c>
+      <c r="N155">
+        <f t="shared" si="11"/>
+        <v>-3.2204771999999999</v>
+      </c>
+      <c r="O155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A156">
         <v>0.57613599999999998</v>
       </c>
@@ -2129,8 +5562,30 @@
       <c r="C156">
         <v>0</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G156">
+        <f t="shared" si="8"/>
+        <v>118.0502664</v>
+      </c>
+      <c r="H156">
+        <f t="shared" si="9"/>
+        <v>-4.3957196999999999</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="M156">
+        <f t="shared" si="10"/>
+        <v>82.617902400000006</v>
+      </c>
+      <c r="N156">
+        <f t="shared" si="11"/>
+        <v>-3.0763601999999999</v>
+      </c>
+      <c r="O156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A157">
         <v>0.59143800000000002</v>
       </c>
@@ -2140,8 +5595,30 @@
       <c r="C157">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G157">
+        <f t="shared" si="8"/>
+        <v>121.18564620000001</v>
+      </c>
+      <c r="H157">
+        <f t="shared" si="9"/>
+        <v>-4.1920491000000002</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="M157">
+        <f t="shared" si="10"/>
+        <v>84.812209200000012</v>
+      </c>
+      <c r="N157">
+        <f t="shared" si="11"/>
+        <v>-2.9338206000000002</v>
+      </c>
+      <c r="O157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A158">
         <v>0.60666299999999995</v>
       </c>
@@ -2151,8 +5628,30 @@
       <c r="C158">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G158">
+        <f t="shared" si="8"/>
+        <v>124.30524869999999</v>
+      </c>
+      <c r="H158">
+        <f t="shared" si="9"/>
+        <v>-3.9912471000000003</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="M158">
+        <f t="shared" si="10"/>
+        <v>86.99547419999999</v>
+      </c>
+      <c r="N158">
+        <f t="shared" si="11"/>
+        <v>-2.7932885999999999</v>
+      </c>
+      <c r="O158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A159">
         <v>0.62179700000000004</v>
       </c>
@@ -2162,8 +5661,30 @@
       <c r="C159">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G159">
+        <f t="shared" si="8"/>
+        <v>127.40620530000001</v>
+      </c>
+      <c r="H159">
+        <f t="shared" si="9"/>
+        <v>-3.7941332999999999</v>
+      </c>
+      <c r="I159">
+        <v>0</v>
+      </c>
+      <c r="M159">
+        <f t="shared" si="10"/>
+        <v>89.16568980000001</v>
+      </c>
+      <c r="N159">
+        <f t="shared" si="11"/>
+        <v>-2.6553377999999999</v>
+      </c>
+      <c r="O159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A160">
         <v>0.63682399999999995</v>
       </c>
@@ -2173,8 +5694,30 @@
       <c r="C160">
         <v>0</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G160">
+        <f t="shared" si="8"/>
+        <v>130.4852376</v>
+      </c>
+      <c r="H160">
+        <f t="shared" si="9"/>
+        <v>-3.6007076999999996</v>
+      </c>
+      <c r="I160">
+        <v>0</v>
+      </c>
+      <c r="M160">
+        <f t="shared" si="10"/>
+        <v>91.320561599999991</v>
+      </c>
+      <c r="N160">
+        <f t="shared" si="11"/>
+        <v>-2.5199681999999997</v>
+      </c>
+      <c r="O160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A161">
         <v>0.65173000000000003</v>
       </c>
@@ -2184,8 +5727,30 @@
       <c r="C161">
         <v>0</v>
       </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G161">
+        <f t="shared" si="8"/>
+        <v>133.53947700000001</v>
+      </c>
+      <c r="H161">
+        <f t="shared" si="9"/>
+        <v>-3.4117899</v>
+      </c>
+      <c r="I161">
+        <v>0</v>
+      </c>
+      <c r="M161">
+        <f t="shared" si="10"/>
+        <v>93.458082000000005</v>
+      </c>
+      <c r="N161">
+        <f t="shared" si="11"/>
+        <v>-2.3877533999999998</v>
+      </c>
+      <c r="O161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A162">
         <v>0.66649899999999995</v>
       </c>
@@ -2195,8 +5760,30 @@
       <c r="C162">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G162">
+        <f t="shared" si="8"/>
+        <v>136.56564509999998</v>
+      </c>
+      <c r="H162">
+        <f t="shared" si="9"/>
+        <v>-3.2273799000000003</v>
+      </c>
+      <c r="I162">
+        <v>0</v>
+      </c>
+      <c r="M162">
+        <f t="shared" si="10"/>
+        <v>95.575956599999998</v>
+      </c>
+      <c r="N162">
+        <f t="shared" si="11"/>
+        <v>-2.2586934000000003</v>
+      </c>
+      <c r="O162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A163">
         <v>0.68111900000000003</v>
       </c>
@@ -2206,8 +5793,30 @@
       <c r="C163">
         <v>0</v>
       </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G163">
+        <f t="shared" si="8"/>
+        <v>139.5612831</v>
+      </c>
+      <c r="H163">
+        <f t="shared" si="9"/>
+        <v>-3.0480924000000003</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="M163">
+        <f t="shared" si="10"/>
+        <v>97.672464600000012</v>
+      </c>
+      <c r="N163">
+        <f t="shared" si="11"/>
+        <v>-2.1332184000000001</v>
+      </c>
+      <c r="O163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A164">
         <v>0.695573</v>
       </c>
@@ -2217,8 +5826,30 @@
       <c r="C164">
         <v>0</v>
       </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G164">
+        <f t="shared" si="8"/>
+        <v>142.52290769999999</v>
+      </c>
+      <c r="H164">
+        <f t="shared" si="9"/>
+        <v>-2.8739274000000004</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="M164">
+        <f t="shared" si="10"/>
+        <v>99.745168200000009</v>
+      </c>
+      <c r="N164">
+        <f t="shared" si="11"/>
+        <v>-2.0113284</v>
+      </c>
+      <c r="O164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A165">
         <v>0.70984700000000001</v>
       </c>
@@ -2228,8 +5859,30 @@
       <c r="C165">
         <v>0</v>
       </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G165">
+        <f t="shared" si="8"/>
+        <v>145.44765029999999</v>
+      </c>
+      <c r="H165">
+        <f t="shared" si="9"/>
+        <v>-2.7052947000000001</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+      <c r="M165">
+        <f t="shared" si="10"/>
+        <v>101.7920598</v>
+      </c>
+      <c r="N165">
+        <f t="shared" si="11"/>
+        <v>-1.8933101999999999</v>
+      </c>
+      <c r="O165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A166">
         <v>0.72392800000000002</v>
       </c>
@@ -2239,8 +5892,30 @@
       <c r="C166">
         <v>0</v>
       </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G166">
+        <f t="shared" si="8"/>
+        <v>148.3328472</v>
+      </c>
+      <c r="H166">
+        <f t="shared" si="9"/>
+        <v>-2.5421942999999998</v>
+      </c>
+      <c r="I166">
+        <v>0</v>
+      </c>
+      <c r="M166">
+        <f t="shared" si="10"/>
+        <v>103.81127520000001</v>
+      </c>
+      <c r="N166">
+        <f t="shared" si="11"/>
+        <v>-1.7791638000000001</v>
+      </c>
+      <c r="O166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A167">
         <v>0.73780000000000001</v>
       </c>
@@ -2250,8 +5925,30 @@
       <c r="C167">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G167">
+        <f t="shared" si="8"/>
+        <v>151.17522</v>
+      </c>
+      <c r="H167">
+        <f t="shared" si="9"/>
+        <v>-2.3846262</v>
+      </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
+      <c r="M167">
+        <f t="shared" si="10"/>
+        <v>105.80052000000001</v>
+      </c>
+      <c r="N167">
+        <f t="shared" si="11"/>
+        <v>-1.6688892000000002</v>
+      </c>
+      <c r="O167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A168">
         <v>0.75144900000000003</v>
       </c>
@@ -2261,8 +5958,30 @@
       <c r="C168">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G168">
+        <f t="shared" si="8"/>
+        <v>153.9719001</v>
+      </c>
+      <c r="H168">
+        <f t="shared" si="9"/>
+        <v>-2.2330002000000002</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="M168">
+        <f t="shared" si="10"/>
+        <v>107.7577866</v>
+      </c>
+      <c r="N168">
+        <f t="shared" si="11"/>
+        <v>-1.5627732000000001</v>
+      </c>
+      <c r="O168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A169">
         <v>0.76486299999999996</v>
       </c>
@@ -2272,8 +5991,30 @@
       <c r="C169">
         <v>0</v>
       </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G169">
+        <f t="shared" si="8"/>
+        <v>156.72042869999999</v>
+      </c>
+      <c r="H169">
+        <f t="shared" si="9"/>
+        <v>-2.0871114000000004</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+      <c r="M169">
+        <f t="shared" si="10"/>
+        <v>109.6813542</v>
+      </c>
+      <c r="N169">
+        <f t="shared" si="11"/>
+        <v>-1.4606724000000002</v>
+      </c>
+      <c r="O169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A170">
         <v>0.778026</v>
       </c>
@@ -2283,8 +6024,30 @@
       <c r="C170">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G170">
+        <f t="shared" si="8"/>
+        <v>159.41752740000001</v>
+      </c>
+      <c r="H170">
+        <f t="shared" si="9"/>
+        <v>-1.9469598000000001</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+      <c r="M170">
+        <f t="shared" si="10"/>
+        <v>111.5689284</v>
+      </c>
+      <c r="N170">
+        <f t="shared" si="11"/>
+        <v>-1.3625868000000001</v>
+      </c>
+      <c r="O170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A171">
         <v>0.79092499999999999</v>
       </c>
@@ -2294,8 +6057,30 @@
       <c r="C171">
         <v>0</v>
       </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G171">
+        <f t="shared" si="8"/>
+        <v>162.06053249999999</v>
+      </c>
+      <c r="H171">
+        <f t="shared" si="9"/>
+        <v>-1.8127503000000003</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+      <c r="M171">
+        <f t="shared" si="10"/>
+        <v>113.418645</v>
+      </c>
+      <c r="N171">
+        <f t="shared" si="11"/>
+        <v>-1.2686598000000002</v>
+      </c>
+      <c r="O171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A172">
         <v>0.80354700000000001</v>
       </c>
@@ -2305,8 +6090,30 @@
       <c r="C172">
         <v>0</v>
       </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G172">
+        <f t="shared" si="8"/>
+        <v>164.64678030000002</v>
+      </c>
+      <c r="H172">
+        <f t="shared" si="9"/>
+        <v>-1.6840731000000002</v>
+      </c>
+      <c r="I172">
+        <v>0</v>
+      </c>
+      <c r="M172">
+        <f t="shared" si="10"/>
+        <v>115.22863980000001</v>
+      </c>
+      <c r="N172">
+        <f t="shared" si="11"/>
+        <v>-1.1786046000000001</v>
+      </c>
+      <c r="O172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A173">
         <v>0.81587900000000002</v>
       </c>
@@ -2316,8 +6123,30 @@
       <c r="C173">
         <v>0</v>
       </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G173">
+        <f t="shared" si="8"/>
+        <v>167.1736071</v>
+      </c>
+      <c r="H173">
+        <f t="shared" si="9"/>
+        <v>-1.5611330999999999</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="M173">
+        <f t="shared" si="10"/>
+        <v>116.99704860000001</v>
+      </c>
+      <c r="N173">
+        <f t="shared" si="11"/>
+        <v>-1.0925646</v>
+      </c>
+      <c r="O173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A174">
         <v>0.82790699999999995</v>
       </c>
@@ -2327,8 +6156,30 @@
       <c r="C174">
         <v>0</v>
       </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G174">
+        <f t="shared" si="8"/>
+        <v>169.63814429999999</v>
+      </c>
+      <c r="H174">
+        <f t="shared" si="9"/>
+        <v>-1.4437254000000002</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="M174">
+        <f t="shared" si="10"/>
+        <v>118.72186379999999</v>
+      </c>
+      <c r="N174">
+        <f t="shared" si="11"/>
+        <v>-1.0103964000000001</v>
+      </c>
+      <c r="O174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A175">
         <v>0.83962000000000003</v>
       </c>
@@ -2338,8 +6189,30 @@
       <c r="C175">
         <v>0</v>
       </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G175">
+        <f t="shared" si="8"/>
+        <v>172.038138</v>
+      </c>
+      <c r="H175">
+        <f t="shared" si="9"/>
+        <v>-1.3316451</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+      <c r="M175">
+        <f t="shared" si="10"/>
+        <v>120.40150800000001</v>
+      </c>
+      <c r="N175">
+        <f t="shared" si="11"/>
+        <v>-0.93195660000000002</v>
+      </c>
+      <c r="O175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A176">
         <v>0.85100399999999998</v>
       </c>
@@ -2349,8 +6222,30 @@
       <c r="C176">
         <v>0</v>
       </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G176">
+        <f t="shared" si="8"/>
+        <v>174.3707196</v>
+      </c>
+      <c r="H176">
+        <f t="shared" si="9"/>
+        <v>-1.2250970999999999</v>
+      </c>
+      <c r="I176">
+        <v>0</v>
+      </c>
+      <c r="M176">
+        <f t="shared" si="10"/>
+        <v>122.0339736</v>
+      </c>
+      <c r="N176">
+        <f t="shared" si="11"/>
+        <v>-0.85738860000000006</v>
+      </c>
+      <c r="O176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A177">
         <v>0.86204800000000004</v>
       </c>
@@ -2360,8 +6255,30 @@
       <c r="C177">
         <v>0</v>
       </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G177">
+        <f t="shared" si="8"/>
+        <v>176.63363520000001</v>
+      </c>
+      <c r="H177">
+        <f t="shared" si="9"/>
+        <v>-1.1236716</v>
+      </c>
+      <c r="I177">
+        <v>0</v>
+      </c>
+      <c r="M177">
+        <f t="shared" si="10"/>
+        <v>123.61768320000002</v>
+      </c>
+      <c r="N177">
+        <f t="shared" si="11"/>
+        <v>-0.78640560000000004</v>
+      </c>
+      <c r="O177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A178">
         <v>0.87273900000000004</v>
       </c>
@@ -2371,8 +6288,30 @@
       <c r="C178">
         <v>0</v>
       </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G178">
+        <f t="shared" si="8"/>
+        <v>178.82422110000002</v>
+      </c>
+      <c r="H178">
+        <f t="shared" si="9"/>
+        <v>-1.0273686</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+      <c r="M178">
+        <f t="shared" si="10"/>
+        <v>125.15077260000001</v>
+      </c>
+      <c r="N178">
+        <f t="shared" si="11"/>
+        <v>-0.71900760000000008</v>
+      </c>
+      <c r="O178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A179">
         <v>0.88306700000000005</v>
       </c>
@@ -2382,8 +6321,30 @@
       <c r="C179">
         <v>0</v>
       </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G179">
+        <f t="shared" si="8"/>
+        <v>180.94042830000001</v>
+      </c>
+      <c r="H179">
+        <f t="shared" si="9"/>
+        <v>-0.93598320000000002</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+      <c r="M179">
+        <f t="shared" si="10"/>
+        <v>126.63180780000002</v>
+      </c>
+      <c r="N179">
+        <f t="shared" si="11"/>
+        <v>-0.65505120000000006</v>
+      </c>
+      <c r="O179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A180">
         <v>0.89301900000000001</v>
       </c>
@@ -2393,8 +6354,30 @@
       <c r="C180">
         <v>0</v>
       </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G180">
+        <f t="shared" si="8"/>
+        <v>182.97959310000002</v>
+      </c>
+      <c r="H180">
+        <f t="shared" si="9"/>
+        <v>-0.84951540000000014</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="M180">
+        <f t="shared" si="10"/>
+        <v>128.05892460000001</v>
+      </c>
+      <c r="N180">
+        <f t="shared" si="11"/>
+        <v>-0.59453640000000008</v>
+      </c>
+      <c r="O180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A181">
         <v>0.902586</v>
       </c>
@@ -2404,8 +6387,30 @@
       <c r="C181">
         <v>0</v>
       </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G181">
+        <f t="shared" si="8"/>
+        <v>184.93987140000002</v>
+      </c>
+      <c r="H181">
+        <f t="shared" si="9"/>
+        <v>-0.76776029999999995</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+      <c r="M181">
+        <f t="shared" si="10"/>
+        <v>129.43083240000001</v>
+      </c>
+      <c r="N181">
+        <f t="shared" si="11"/>
+        <v>-0.53731980000000001</v>
+      </c>
+      <c r="O181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A182">
         <v>0.91175600000000001</v>
       </c>
@@ -2415,8 +6420,30 @@
       <c r="C182">
         <v>0</v>
       </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G182">
+        <f t="shared" si="8"/>
+        <v>186.8188044</v>
+      </c>
+      <c r="H182">
+        <f t="shared" si="9"/>
+        <v>-0.69051300000000004</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="M182">
+        <f t="shared" si="10"/>
+        <v>130.74581040000001</v>
+      </c>
+      <c r="N182">
+        <f t="shared" si="11"/>
+        <v>-0.48325800000000002</v>
+      </c>
+      <c r="O182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A183">
         <v>0.92052</v>
       </c>
@@ -2426,8 +6453,30 @@
       <c r="C183">
         <v>0</v>
       </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G183">
+        <f t="shared" si="8"/>
+        <v>188.61454800000001</v>
+      </c>
+      <c r="H183">
+        <f t="shared" si="9"/>
+        <v>-0.61777349999999998</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+      <c r="M183">
+        <f t="shared" si="10"/>
+        <v>132.002568</v>
+      </c>
+      <c r="N183">
+        <f t="shared" si="11"/>
+        <v>-0.43235099999999999</v>
+      </c>
+      <c r="O183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A184">
         <v>0.92886899999999994</v>
       </c>
@@ -2437,8 +6486,30 @@
       <c r="C184">
         <v>0</v>
       </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G184">
+        <f t="shared" si="8"/>
+        <v>190.32525809999999</v>
+      </c>
+      <c r="H184">
+        <f t="shared" si="9"/>
+        <v>-0.54954179999999997</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+      <c r="M184">
+        <f t="shared" si="10"/>
+        <v>133.1998146</v>
+      </c>
+      <c r="N184">
+        <f t="shared" si="11"/>
+        <v>-0.38459880000000002</v>
+      </c>
+      <c r="O184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A185">
         <v>0.93679100000000004</v>
       </c>
@@ -2448,8 +6519,30 @@
       <c r="C185">
         <v>0</v>
       </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G185">
+        <f t="shared" si="8"/>
+        <v>191.94847590000001</v>
+      </c>
+      <c r="H185">
+        <f t="shared" si="9"/>
+        <v>-0.48561300000000002</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="M185">
+        <f t="shared" si="10"/>
+        <v>134.33582940000002</v>
+      </c>
+      <c r="N185">
+        <f t="shared" si="11"/>
+        <v>-0.33985800000000005</v>
+      </c>
+      <c r="O185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A186">
         <v>0.94428000000000001</v>
       </c>
@@ -2459,8 +6552,30 @@
       <c r="C186">
         <v>0</v>
       </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G186">
+        <f t="shared" si="8"/>
+        <v>193.48297200000002</v>
+      </c>
+      <c r="H186">
+        <f t="shared" si="9"/>
+        <v>-0.42598710000000006</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+      <c r="M186">
+        <f t="shared" si="10"/>
+        <v>135.409752</v>
+      </c>
+      <c r="N186">
+        <f t="shared" si="11"/>
+        <v>-0.29812860000000002</v>
+      </c>
+      <c r="O186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A187">
         <v>0.951326</v>
       </c>
@@ -2470,8 +6585,30 @@
       <c r="C187">
         <v>0</v>
       </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G187">
+        <f t="shared" si="8"/>
+        <v>194.92669739999999</v>
+      </c>
+      <c r="H187">
+        <f t="shared" si="9"/>
+        <v>-0.37025430000000004</v>
+      </c>
+      <c r="I187">
+        <v>0</v>
+      </c>
+      <c r="M187">
+        <f t="shared" si="10"/>
+        <v>136.42014840000002</v>
+      </c>
+      <c r="N187">
+        <f t="shared" si="11"/>
+        <v>-0.25912380000000002</v>
+      </c>
+      <c r="O187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A188">
         <v>0.95792200000000005</v>
       </c>
@@ -2481,8 +6618,30 @@
       <c r="C188">
         <v>0</v>
       </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G188">
+        <f t="shared" si="8"/>
+        <v>196.27821780000002</v>
+      </c>
+      <c r="H188">
+        <f t="shared" si="9"/>
+        <v>-0.31882440000000001</v>
+      </c>
+      <c r="I188">
+        <v>0</v>
+      </c>
+      <c r="M188">
+        <f t="shared" si="10"/>
+        <v>137.36601480000002</v>
+      </c>
+      <c r="N188">
+        <f t="shared" si="11"/>
+        <v>-0.22313040000000003</v>
+      </c>
+      <c r="O188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A189">
         <v>0.96406000000000003</v>
       </c>
@@ -2492,8 +6651,30 @@
       <c r="C189">
         <v>0</v>
       </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G189">
+        <f t="shared" si="8"/>
+        <v>197.53589400000001</v>
+      </c>
+      <c r="H189">
+        <f t="shared" si="9"/>
+        <v>-0.27108270000000001</v>
+      </c>
+      <c r="I189">
+        <v>0</v>
+      </c>
+      <c r="M189">
+        <f t="shared" si="10"/>
+        <v>138.24620400000001</v>
+      </c>
+      <c r="N189">
+        <f t="shared" si="11"/>
+        <v>-0.1897182</v>
+      </c>
+      <c r="O189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A190">
         <v>0.96973399999999998</v>
       </c>
@@ -2503,8 +6684,30 @@
       <c r="C190">
         <v>0</v>
       </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G190">
+        <f t="shared" si="8"/>
+        <v>198.6984966</v>
+      </c>
+      <c r="H190">
+        <f t="shared" si="9"/>
+        <v>-0.22764390000000001</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+      <c r="M190">
+        <f t="shared" si="10"/>
+        <v>139.05985559999999</v>
+      </c>
+      <c r="N190">
+        <f t="shared" si="11"/>
+        <v>-0.1593174</v>
+      </c>
+      <c r="O190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A191">
         <v>0.97493600000000002</v>
       </c>
@@ -2514,8 +6717,30 @@
       <c r="C191">
         <v>0</v>
       </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G191">
+        <f t="shared" si="8"/>
+        <v>199.76438640000001</v>
+      </c>
+      <c r="H191">
+        <f t="shared" si="9"/>
+        <v>-0.18789329999999999</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="M191">
+        <f t="shared" si="10"/>
+        <v>139.80582240000001</v>
+      </c>
+      <c r="N191">
+        <f t="shared" si="11"/>
+        <v>-0.1314978</v>
+      </c>
+      <c r="O191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A192">
         <v>0.979661</v>
       </c>
@@ -2525,8 +6750,30 @@
       <c r="C192">
         <v>0</v>
       </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G192">
+        <f t="shared" si="8"/>
+        <v>200.73253890000001</v>
+      </c>
+      <c r="H192">
+        <f t="shared" si="9"/>
+        <v>-0.1520358</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+      <c r="M192">
+        <f t="shared" si="10"/>
+        <v>140.4833874</v>
+      </c>
+      <c r="N192">
+        <f t="shared" si="11"/>
+        <v>-0.10640280000000001</v>
+      </c>
+      <c r="O192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A193">
         <v>0.98390299999999997</v>
       </c>
@@ -2536,8 +6783,30 @@
       <c r="C193">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G193">
+        <f t="shared" si="8"/>
+        <v>201.60172470000001</v>
+      </c>
+      <c r="H193">
+        <f t="shared" si="9"/>
+        <v>-0.12007140000000001</v>
+      </c>
+      <c r="I193">
+        <v>0</v>
+      </c>
+      <c r="M193">
+        <f t="shared" si="10"/>
+        <v>141.09169019999999</v>
+      </c>
+      <c r="N193">
+        <f t="shared" si="11"/>
+        <v>-8.4032400000000007E-2</v>
+      </c>
+      <c r="O193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A194">
         <v>0.98765800000000004</v>
       </c>
@@ -2547,8 +6816,30 @@
       <c r="C194">
         <v>0</v>
       </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G194">
+        <f t="shared" ref="G194:G201" si="12">$F$1*$A194</f>
+        <v>202.37112420000003</v>
+      </c>
+      <c r="H194">
+        <f t="shared" ref="H194:H201" si="13">$F$1*$B194</f>
+        <v>-9.1795200000000007E-2</v>
+      </c>
+      <c r="I194">
+        <v>0</v>
+      </c>
+      <c r="M194">
+        <f t="shared" ref="M194:M201" si="14">$L$1*$A194</f>
+        <v>141.63015720000001</v>
+      </c>
+      <c r="N194">
+        <f t="shared" ref="N194:N201" si="15">$L$1*$B194</f>
+        <v>-6.42432E-2</v>
+      </c>
+      <c r="O194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A195">
         <v>0.99092100000000005</v>
       </c>
@@ -2558,8 +6849,30 @@
       <c r="C195">
         <v>0</v>
       </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G195">
+        <f t="shared" si="12"/>
+        <v>203.03971290000001</v>
+      </c>
+      <c r="H195">
+        <f t="shared" si="13"/>
+        <v>-6.7412100000000003E-2</v>
+      </c>
+      <c r="I195">
+        <v>0</v>
+      </c>
+      <c r="M195">
+        <f t="shared" si="14"/>
+        <v>142.09807140000001</v>
+      </c>
+      <c r="N195">
+        <f t="shared" si="15"/>
+        <v>-4.7178600000000001E-2</v>
+      </c>
+      <c r="O195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A196">
         <v>0.99368800000000002</v>
       </c>
@@ -2569,8 +6882,30 @@
       <c r="C196">
         <v>0</v>
       </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G196">
+        <f t="shared" si="12"/>
+        <v>203.60667120000002</v>
+      </c>
+      <c r="H196">
+        <f t="shared" si="13"/>
+        <v>-4.6717200000000007E-2</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+      <c r="M196">
+        <f t="shared" si="14"/>
+        <v>142.49485920000001</v>
+      </c>
+      <c r="N196">
+        <f t="shared" si="15"/>
+        <v>-3.2695200000000001E-2</v>
+      </c>
+      <c r="O196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A197">
         <v>0.99595699999999998</v>
       </c>
@@ -2580,8 +6915,30 @@
       <c r="C197">
         <v>0</v>
       </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G197">
+        <f t="shared" si="12"/>
+        <v>204.0715893</v>
+      </c>
+      <c r="H197">
+        <f t="shared" si="13"/>
+        <v>-2.9915400000000002E-2</v>
+      </c>
+      <c r="I197">
+        <v>0</v>
+      </c>
+      <c r="M197">
+        <f t="shared" si="14"/>
+        <v>142.82023380000001</v>
+      </c>
+      <c r="N197">
+        <f t="shared" si="15"/>
+        <v>-2.0936400000000001E-2</v>
+      </c>
+      <c r="O197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A198">
         <v>0.99772400000000006</v>
       </c>
@@ -2591,8 +6948,30 @@
       <c r="C198">
         <v>0</v>
       </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G198">
+        <f t="shared" si="12"/>
+        <v>204.43364760000003</v>
+      </c>
+      <c r="H198">
+        <f t="shared" si="13"/>
+        <v>-1.6801800000000002E-2</v>
+      </c>
+      <c r="I198">
+        <v>0</v>
+      </c>
+      <c r="M198">
+        <f t="shared" si="14"/>
+        <v>143.07362160000002</v>
+      </c>
+      <c r="N198">
+        <f t="shared" si="15"/>
+        <v>-1.17588E-2</v>
+      </c>
+      <c r="O198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A199">
         <v>0.99898799999999999</v>
       </c>
@@ -2602,8 +6981,30 @@
       <c r="C199">
         <v>0</v>
       </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G199">
+        <f t="shared" si="12"/>
+        <v>204.6926412</v>
+      </c>
+      <c r="H199">
+        <f t="shared" si="13"/>
+        <v>-7.5813E-3</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="M199">
+        <f t="shared" si="14"/>
+        <v>143.2548792</v>
+      </c>
+      <c r="N199">
+        <f t="shared" si="15"/>
+        <v>-5.3058000000000003E-3</v>
+      </c>
+      <c r="O199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A200">
         <v>0.99974700000000005</v>
       </c>
@@ -2613,8 +7014,30 @@
       <c r="C200">
         <v>0</v>
       </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G200">
+        <f t="shared" si="12"/>
+        <v>204.84816030000002</v>
+      </c>
+      <c r="H200">
+        <f t="shared" si="13"/>
+        <v>-1.8441E-3</v>
+      </c>
+      <c r="I200">
+        <v>0</v>
+      </c>
+      <c r="M200">
+        <f t="shared" si="14"/>
+        <v>143.36371980000001</v>
+      </c>
+      <c r="N200">
+        <f t="shared" si="15"/>
+        <v>-1.2906E-3</v>
+      </c>
+      <c r="O200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A201">
         <v>1</v>
       </c>
@@ -2622,6 +7045,28 @@
         <v>0</v>
       </c>
       <c r="C201">
+        <v>0</v>
+      </c>
+      <c r="G201">
+        <f t="shared" si="12"/>
+        <v>204.9</v>
+      </c>
+      <c r="H201">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="I201">
+        <v>0</v>
+      </c>
+      <c r="M201">
+        <f t="shared" si="14"/>
+        <v>143.4</v>
+      </c>
+      <c r="N201">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O201">
         <v>0</v>
       </c>
     </row>
